--- a/04_Figures/F06_prediction/modules/acute/enet/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/acute/enet/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -146,43 +146,37 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_blue</t>
+    <t xml:space="preserve">ME_brown</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_purple</t>
+    <t xml:space="preserve">ME_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_red</t>
   </si>
   <si>
     <t xml:space="preserve">ME_black</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_green</t>
+    <t xml:space="preserve">ME_blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_greenyellow</t>
   </si>
   <si>
     <t xml:space="preserve">ME_magenta</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_red</t>
+    <t xml:space="preserve">ME_purple</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
   </si>
   <si>
     <t xml:space="preserve">ME_yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_greenyellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
 </sst>
 </file>
@@ -569,16 +563,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.255166892363626</v>
+        <v>-0.188364748090807</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.978571428571428</v>
+        <v>-0.925</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -602,28 +596,28 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.255166892363626</v>
+        <v>-0.188364748090807</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.978571428571428</v>
+        <v>-0.925</v>
       </c>
       <c r="J3" t="n">
-        <v>0.621890547263682</v>
+        <v>0.522388059701492</v>
       </c>
       <c r="K3" t="n">
-        <v>0.497512437810945</v>
+        <v>0.348258706467662</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.371320297898219</v>
+        <v>-0.727402692068061</v>
       </c>
       <c r="M3" t="n">
-        <v>0.643584147919429</v>
+        <v>1.65140173921837</v>
       </c>
     </row>
     <row r="4">
@@ -643,13 +637,13 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.499741852529859</v>
       </c>
       <c r="I4" t="n">
         <v>-1</v>
@@ -676,28 +670,28 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.499741852529859</v>
       </c>
       <c r="I5" t="n">
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.238805970149254</v>
+        <v>0.800995024875622</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.417911871136649</v>
+        <v>-0.564392265567674</v>
       </c>
       <c r="M5" t="n">
-        <v>0.894978615737611</v>
+        <v>1.50936519144489</v>
       </c>
     </row>
     <row r="6">
@@ -717,7 +711,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -750,7 +744,7 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
@@ -762,16 +756,16 @@
         <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.492537313432836</v>
+        <v>0.467661691542289</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.409346831092307</v>
+        <v>-0.881552300851242</v>
       </c>
       <c r="M7" t="n">
-        <v>0.808770908468774</v>
+        <v>4.38986487880533</v>
       </c>
     </row>
     <row r="8">
@@ -791,16 +785,16 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.496018041320871</v>
+        <v>-0.650588876315223</v>
       </c>
       <c r="I8" t="n">
-        <v>0.714285714285714</v>
+        <v>-0.717857142857143</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -824,28 +818,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>0.496018041320871</v>
+        <v>-0.650588876315223</v>
       </c>
       <c r="I9" t="n">
-        <v>0.714285714285714</v>
+        <v>-0.717857142857143</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0199004975124378</v>
+        <v>0.850746268656716</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0199004975124378</v>
+        <v>0.17910447761194</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.278336585306488</v>
+        <v>-0.56940029804768</v>
       </c>
       <c r="M9" t="n">
-        <v>0.364953553604116</v>
+        <v>1.42068962165079</v>
       </c>
     </row>
     <row r="10">
@@ -865,13 +859,13 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.426561368745532</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I10" t="n">
         <v>-0.996415759077198</v>
@@ -898,28 +892,28 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.426561368745532</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I11" t="n">
         <v>-0.996415759077198</v>
       </c>
       <c r="J11" t="n">
-        <v>0.776119402985075</v>
+        <v>0.194029850746269</v>
       </c>
       <c r="K11" t="n">
-        <v>0.716417910447761</v>
+        <v>0.63681592039801</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.356904877195809</v>
+        <v>-0.598169514333446</v>
       </c>
       <c r="M11" t="n">
-        <v>0.452453617226983</v>
+        <v>1.68877947600154</v>
       </c>
     </row>
     <row r="12">
@@ -939,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -972,7 +966,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
@@ -984,16 +978,16 @@
         <v>-1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3681592039801</v>
+        <v>0.383084577114428</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.281581160452672</v>
+        <v>-0.397576634145466</v>
       </c>
       <c r="M13" t="n">
-        <v>0.354285445230893</v>
+        <v>0.687794172289692</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.14795918367347</v>
+        <v>-5.77330106488166</v>
       </c>
     </row>
     <row r="4">
@@ -1048,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.131095694206079</v>
       </c>
     </row>
     <row r="5">
@@ -1059,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.279145945368278</v>
+        <v>-1.12955704737026</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.155668922173634</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="7">
@@ -1081,7 +1075,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.171988386424339</v>
       </c>
     </row>
     <row r="8">
@@ -1103,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.262880328731841</v>
+        <v>-0.235718526457808</v>
       </c>
     </row>
     <row r="10">
@@ -1147,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.110432910007867</v>
+        <v>-0.176050786566205</v>
       </c>
     </row>
     <row r="14">
@@ -1158,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.838514011928732</v>
+        <v>-0.473997923168071</v>
       </c>
     </row>
     <row r="15">
@@ -1180,7 +1174,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.379755457108412</v>
+        <v>-0.296728379973731</v>
       </c>
     </row>
     <row r="17">
@@ -1202,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.188622106353866</v>
+        <v>-0.0193634415756625</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.445082029049029</v>
+        <v>-0.401123808909751</v>
       </c>
     </row>
     <row r="20">
@@ -1224,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.547911060772915</v>
+        <v>-6.6124354382462</v>
       </c>
     </row>
     <row r="21">
@@ -1235,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.26820013687368</v>
+        <v>-0.279193857814137</v>
       </c>
     </row>
     <row r="22">
@@ -1246,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.48455275013419</v>
+        <v>-0.280044054701958</v>
       </c>
     </row>
     <row r="23">
@@ -1257,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.04482564027839</v>
+        <v>-0.791921039045731</v>
       </c>
     </row>
     <row r="24">
@@ -1268,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.544625306337616</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="25">
@@ -1301,7 +1295,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.569217701861415</v>
       </c>
     </row>
     <row r="28">
@@ -1312,7 +1306,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.155987184714122</v>
       </c>
     </row>
     <row r="29">
@@ -1323,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.438868690053083</v>
+        <v>-0.624917835373913</v>
       </c>
     </row>
     <row r="30">
@@ -1345,7 +1339,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.240640715019485</v>
+        <v>-0.137433260653793</v>
       </c>
     </row>
     <row r="32">
@@ -1367,7 +1361,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.322418376600835</v>
+        <v>-0.328843676202293</v>
       </c>
     </row>
     <row r="34">
@@ -1378,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.280473167467609</v>
+        <v>-0.17134209244381</v>
       </c>
     </row>
     <row r="35">
@@ -1389,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.610338149332542</v>
+        <v>-0.414303047788847</v>
       </c>
     </row>
     <row r="36">
@@ -1400,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.42013177444434</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="37">
@@ -1411,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.082059386491705</v>
+        <v>-0.0434538264667343</v>
       </c>
     </row>
     <row r="38">
@@ -1422,7 +1416,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>0.376535802782794</v>
+        <v>-0.828123983554237</v>
       </c>
     </row>
     <row r="39">
@@ -1444,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.138979371851308</v>
+        <v>-0.174378955644394</v>
       </c>
     </row>
     <row r="41">
@@ -1455,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.203750205749824</v>
+        <v>-0.5094018258172</v>
       </c>
     </row>
     <row r="42">
@@ -1466,7 +1460,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.73837688787369</v>
       </c>
     </row>
     <row r="43">
@@ -1488,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.189887125415356</v>
+        <v>-0.816857164425055</v>
       </c>
     </row>
     <row r="45">
@@ -1499,7 +1493,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>-3.81100676595348</v>
+        <v>-4.43550293412322</v>
       </c>
     </row>
     <row r="46">
@@ -1510,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.16506862412492</v>
+        <v>-0.182908547729228</v>
       </c>
     </row>
     <row r="47">
@@ -1521,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.406864623942427</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="48">
@@ -1532,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.229182357606259</v>
+        <v>-0.213182454311384</v>
       </c>
     </row>
     <row r="49">
@@ -1543,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0992475144735603</v>
+        <v>-0.463135250963408</v>
       </c>
     </row>
     <row r="50">
@@ -1554,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.14954804471808</v>
       </c>
     </row>
     <row r="51">
@@ -1565,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.213473292497738</v>
       </c>
     </row>
     <row r="52">
@@ -1576,7 +1570,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.812892065305919</v>
       </c>
     </row>
     <row r="53">
@@ -1587,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>0.538548919880713</v>
+        <v>-0.320012258143406</v>
       </c>
     </row>
     <row r="54">
@@ -1598,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0556287711506238</v>
+        <v>-0.193854542200274</v>
       </c>
     </row>
     <row r="55">
@@ -1609,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.170625381054367</v>
+        <v>-0.182311539666469</v>
       </c>
     </row>
     <row r="56">
@@ -1620,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.656487729527733</v>
+        <v>-0.779171033783022</v>
       </c>
     </row>
     <row r="57">
@@ -1631,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.95238961484198</v>
       </c>
     </row>
     <row r="58">
@@ -1642,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.651463806682284</v>
+        <v>-0.187840695020937</v>
       </c>
     </row>
     <row r="59">
@@ -1664,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.39721345202348</v>
+        <v>-4.23869631815195</v>
       </c>
     </row>
     <row r="61">
@@ -1675,7 +1669,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.283489473163173</v>
+        <v>-0.379247684770092</v>
       </c>
     </row>
     <row r="62">
@@ -1686,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.46179400013025</v>
       </c>
     </row>
     <row r="63">
@@ -1719,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-3.03428153036026</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="66">
@@ -1730,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.769935497986017</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="67">
@@ -1741,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.420283386137672</v>
       </c>
     </row>
     <row r="68">
@@ -1752,7 +1746,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.197509089654935</v>
+        <v>-0.159141859457646</v>
       </c>
     </row>
     <row r="69">
@@ -1763,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.252568342272423</v>
+        <v>-0.681736356685982</v>
       </c>
     </row>
     <row r="70">
@@ -1774,7 +1768,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.647996136769807</v>
+        <v>-0.58747936207018</v>
       </c>
     </row>
     <row r="71">
@@ -1785,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.243314262371947</v>
+        <v>-0.364211946494656</v>
       </c>
     </row>
     <row r="72">
@@ -1796,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.199523231796038</v>
+        <v>-0.173193779286288</v>
       </c>
     </row>
     <row r="73">
@@ -1807,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.19695707088401</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="74">
@@ -1818,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.16281994767103</v>
+        <v>-0.823366809436082</v>
       </c>
     </row>
     <row r="75">
@@ -1829,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.599013785040762</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="76">
@@ -1840,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.34992297535668</v>
+        <v>-0.236328780982173</v>
       </c>
     </row>
     <row r="77">
@@ -1851,7 +1845,7 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.14795918367347</v>
+        <v>-14.4794333892437</v>
       </c>
     </row>
     <row r="78">
@@ -1862,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.156748734877513</v>
       </c>
     </row>
     <row r="79">
@@ -1873,7 +1867,7 @@
         <v>16</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.328273848613036</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="80">
@@ -1884,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.752099528652838</v>
+        <v>-0.509622273908942</v>
       </c>
     </row>
     <row r="81">
@@ -1895,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>0.240681569886155</v>
+        <v>-0.199902373248753</v>
       </c>
     </row>
     <row r="82">
@@ -1906,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.215335094083005</v>
+        <v>-0.530834522186872</v>
       </c>
     </row>
     <row r="83">
@@ -1917,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.270210953278656</v>
+        <v>-4.13892388741733</v>
       </c>
     </row>
     <row r="84">
@@ -1928,7 +1922,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="n">
-        <v>-1.28566340148522</v>
+        <v>-0.516821077811941</v>
       </c>
     </row>
     <row r="85">
@@ -1939,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.640634111822523</v>
       </c>
     </row>
     <row r="86">
@@ -1961,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.16703643937133</v>
+        <v>-0.143862439476412</v>
       </c>
     </row>
     <row r="88">
@@ -1983,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.34164931058965</v>
       </c>
     </row>
     <row r="90">
@@ -1994,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-1.00803663735222</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="91">
@@ -2005,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.36238609957295</v>
       </c>
     </row>
     <row r="92">
@@ -2016,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.563474766759135</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="93">
@@ -2038,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.32400756139464</v>
+        <v>-0.390257383129716</v>
       </c>
     </row>
     <row r="95">
@@ -2049,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>0.26489537560357</v>
+        <v>0.353383912996223</v>
       </c>
     </row>
     <row r="96">
@@ -2060,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.613993102599923</v>
+        <v>-0.60193425114594</v>
       </c>
     </row>
     <row r="97">
@@ -2071,7 +2065,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.175022478950987</v>
       </c>
     </row>
     <row r="98">
@@ -2082,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.588410560060237</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="99">
@@ -2093,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.316822938779282</v>
+        <v>-4.79974047411546</v>
       </c>
     </row>
     <row r="100">
@@ -2104,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.659155652325664</v>
       </c>
     </row>
     <row r="101">
@@ -2137,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.248173431004493</v>
+        <v>-0.16573082167438</v>
       </c>
     </row>
     <row r="104">
@@ -2148,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.464810921645847</v>
+        <v>-0.14208801950196</v>
       </c>
     </row>
     <row r="105">
@@ -2159,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.614040391930207</v>
+        <v>-0.507064214929426</v>
       </c>
     </row>
     <row r="106">
@@ -2170,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.242929472341731</v>
+        <v>-0.340014937970194</v>
       </c>
     </row>
     <row r="107">
@@ -2192,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.279235267456883</v>
+        <v>-0.230785548569935</v>
       </c>
     </row>
     <row r="109">
@@ -2203,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>0.255778376409373</v>
+        <v>-0.656554252677841</v>
       </c>
     </row>
     <row r="110">
@@ -2214,7 +2208,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.15939816211575</v>
       </c>
     </row>
     <row r="111">
@@ -2236,7 +2230,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.261698933272397</v>
+        <v>-0.165055029724328</v>
       </c>
     </row>
     <row r="113">
@@ -2247,7 +2241,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.398662203287506</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="114">
@@ -2269,7 +2263,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.229735987834903</v>
+        <v>-0.182777230463156</v>
       </c>
     </row>
     <row r="116">
@@ -2280,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.19593840356172</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2285,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.236576258839493</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="118">
@@ -2302,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.295426055562697</v>
+        <v>-7.82128595561446</v>
       </c>
     </row>
     <row r="119">
@@ -2324,7 +2318,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.239489949057333</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="121">
@@ -2335,7 +2329,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.14795918367347</v>
+        <v>-5.1352300191309</v>
       </c>
     </row>
     <row r="122">
@@ -2346,7 +2340,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.213573546891372</v>
+        <v>-0.333323268422051</v>
       </c>
     </row>
     <row r="123">
@@ -2368,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.296480704511651</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="125">
@@ -2379,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.125687319647434</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="126">
@@ -2390,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.187534500450437</v>
+        <v>-0.188856323625059</v>
       </c>
     </row>
     <row r="127">
@@ -2401,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.314501249285602</v>
+        <v>-0.387202223014192</v>
       </c>
     </row>
     <row r="128">
@@ -2412,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.300485064126039</v>
+        <v>-0.373605318951601</v>
       </c>
     </row>
     <row r="129">
@@ -2434,7 +2428,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.156127086082684</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="131">
@@ -2445,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.14795918367347</v>
+        <v>-4.22770825128221</v>
       </c>
     </row>
     <row r="132">
@@ -2456,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.287156776383998</v>
+        <v>-0.288563021361971</v>
       </c>
     </row>
     <row r="133">
@@ -2489,7 +2483,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.886325033103187</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="136">
@@ -2500,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>-1.52416016819059</v>
+        <v>-1.2042916156461</v>
       </c>
     </row>
     <row r="137">
@@ -2511,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.326995745856229</v>
+        <v>-0.191956518869284</v>
       </c>
     </row>
     <row r="138">
@@ -2522,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.108676910852776</v>
+        <v>-0.254783650679642</v>
       </c>
     </row>
     <row r="139">
@@ -2533,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.196800295907462</v>
       </c>
     </row>
     <row r="140">
@@ -2544,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.241140327154223</v>
+        <v>-0.211527060543346</v>
       </c>
     </row>
     <row r="141">
@@ -2577,7 +2571,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.993264181912134</v>
       </c>
     </row>
     <row r="144">
@@ -2588,7 +2582,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.19525060415606</v>
       </c>
     </row>
     <row r="145">
@@ -2599,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.17680961378945</v>
+        <v>-0.166761911248272</v>
       </c>
     </row>
     <row r="146">
@@ -2610,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.958184746287025</v>
+        <v>-0.542339494299291</v>
       </c>
     </row>
     <row r="147">
@@ -2621,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.182747481989719</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="148">
@@ -2643,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.21190186023907</v>
+        <v>-1.13901845051379</v>
       </c>
     </row>
     <row r="150">
@@ -2654,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.302939176133363</v>
+        <v>-0.372153418930853</v>
       </c>
     </row>
     <row r="151">
@@ -2665,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.204162452135237</v>
+        <v>-0.320713574849196</v>
       </c>
     </row>
     <row r="152">
@@ -2676,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.663810655143327</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="153">
@@ -2687,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-2.10068411174409</v>
+        <v>-0.188492599818652</v>
       </c>
     </row>
     <row r="154">
@@ -2698,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.167209838397449</v>
       </c>
     </row>
     <row r="155">
@@ -2720,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.770718093182133</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="157">
@@ -2731,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>0.172051192365456</v>
+        <v>-0.313646258477852</v>
       </c>
     </row>
     <row r="158">
@@ -2742,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.515272431590049</v>
       </c>
     </row>
     <row r="159">
@@ -2764,7 +2758,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.379265713969797</v>
+        <v>-0.487422434791857</v>
       </c>
     </row>
     <row r="161">
@@ -2775,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.80307247057073</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="162">
@@ -2797,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.0461267416522482</v>
+        <v>-0.207934490026433</v>
       </c>
     </row>
     <row r="164">
@@ -2808,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.273096684715481</v>
+        <v>-0.218376516280865</v>
       </c>
     </row>
     <row r="165">
@@ -2841,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>-5.22274876106395</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="168">
@@ -2852,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.199049257974733</v>
+        <v>-4.37103712688756</v>
       </c>
     </row>
     <row r="169">
@@ -2863,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.0918400504335013</v>
+        <v>0.0448784648193049</v>
       </c>
     </row>
     <row r="170">
@@ -2874,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.311663259216746</v>
+        <v>-0.183368229165597</v>
       </c>
     </row>
     <row r="171">
@@ -2885,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.334190624865779</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="172">
@@ -2896,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.64060328434535</v>
+        <v>-2.53523051387885</v>
       </c>
     </row>
     <row r="173">
@@ -2907,7 +2901,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-2.30516355145935</v>
+        <v>-1.78251126275583</v>
       </c>
     </row>
     <row r="174">
@@ -2918,7 +2912,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.435044380533009</v>
+        <v>-8.85099839838067</v>
       </c>
     </row>
     <row r="175">
@@ -2929,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.332185622436387</v>
+        <v>-0.351479974793864</v>
       </c>
     </row>
     <row r="176">
@@ -2984,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.668838290694238</v>
+        <v>-0.199171856824286</v>
       </c>
     </row>
     <row r="181">
@@ -2995,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0703979828320173</v>
+        <v>-0.283999471082241</v>
       </c>
     </row>
     <row r="182">
@@ -3006,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.385358246268104</v>
+        <v>-0.159106451685122</v>
       </c>
     </row>
     <row r="183">
@@ -3017,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>0.187943104722558</v>
+        <v>0.425389909675298</v>
       </c>
     </row>
     <row r="184">
@@ -3028,7 +3022,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.15950318804449</v>
+        <v>-1.51319544047748</v>
       </c>
     </row>
     <row r="185">
@@ -3050,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.257219525921667</v>
+        <v>-1.47878607206839</v>
       </c>
     </row>
     <row r="187">
@@ -3061,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.180868452253339</v>
+        <v>-0.246400332691569</v>
       </c>
     </row>
     <row r="188">
@@ -3072,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.16547532364684</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="189">
@@ -3083,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.299397589254151</v>
+        <v>-0.347351284516574</v>
       </c>
     </row>
     <row r="190">
@@ -3094,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.17052524032755</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="191">
@@ -3105,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.612256693709619</v>
+        <v>-0.727267474976502</v>
       </c>
     </row>
     <row r="192">
@@ -3116,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.502814794005944</v>
+        <v>0.625650930469765</v>
       </c>
     </row>
     <row r="193">
@@ -3138,7 +3132,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.337089876078103</v>
+        <v>-0.170780911779571</v>
       </c>
     </row>
     <row r="195">
@@ -3149,7 +3143,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.441774663819586</v>
+        <v>-0.179919472930231</v>
       </c>
     </row>
     <row r="196">
@@ -3160,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-4.435596792545</v>
+        <v>-0.440901177548317</v>
       </c>
     </row>
     <row r="197">
@@ -3171,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.176636574640979</v>
+        <v>-0.205192705479313</v>
       </c>
     </row>
     <row r="198">
@@ -3193,7 +3187,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.104225724337607</v>
+        <v>-4.23146786060045</v>
       </c>
     </row>
     <row r="200">
@@ -3204,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.173375174805951</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="201">
@@ -3215,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.114978453792179</v>
+        <v>-1.08643013013743</v>
       </c>
     </row>
     <row r="202">
@@ -3226,7 +3220,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-1.88715682483628</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="203">
@@ -3237,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.438172361679823</v>
+        <v>-1.26963605530619</v>
       </c>
     </row>
     <row r="204">
@@ -3248,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.19094744936342</v>
+        <v>-0.193505445013966</v>
       </c>
     </row>
     <row r="205">
@@ -3259,7 +3253,7 @@
         <v>16</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.14795918367347</v>
+        <v>0.619228941727886</v>
       </c>
     </row>
     <row r="206">
@@ -3270,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.834247060783364</v>
+        <v>-2.21610939856766</v>
       </c>
     </row>
     <row r="207">
@@ -3281,7 +3275,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.58061956922329</v>
       </c>
     </row>
     <row r="208">
@@ -3292,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.163587162167184</v>
+        <v>-0.168785660566857</v>
       </c>
     </row>
     <row r="209">
@@ -3303,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.80532174603315</v>
+        <v>-0.351713023047346</v>
       </c>
     </row>
     <row r="210">
@@ -3325,7 +3319,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.600142893808234</v>
+        <v>-0.48846810939818</v>
       </c>
     </row>
     <row r="212">
@@ -3336,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-4.27548255580184</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="213">
@@ -3347,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.103874938012738</v>
+        <v>-0.378007346158858</v>
       </c>
     </row>
     <row r="214">
@@ -3358,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>0.13254254870263</v>
+        <v>0.497749667425687</v>
       </c>
     </row>
     <row r="215">
@@ -3369,7 +3363,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.165429663748605</v>
+        <v>-0.269858977177965</v>
       </c>
     </row>
     <row r="216">
@@ -3380,7 +3374,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-2.24422269193344</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="217">
@@ -3402,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.177062860803651</v>
+        <v>-0.089927371977365</v>
       </c>
     </row>
     <row r="219">
@@ -3413,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.323624040199906</v>
+        <v>-0.228646068034531</v>
       </c>
     </row>
     <row r="220">
@@ -3424,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.446809428561934</v>
+        <v>-0.220748956626272</v>
       </c>
     </row>
     <row r="221">
@@ -3446,7 +3440,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.792553999305077</v>
+        <v>-0.197076828632192</v>
       </c>
     </row>
     <row r="223">
@@ -3512,7 +3506,7 @@
         <v>16</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.204080463925115</v>
+        <v>-0.216282478736384</v>
       </c>
     </row>
     <row r="229">
@@ -3523,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.602599334061006</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="230">
@@ -3545,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.41311241047223</v>
+        <v>-0.791102751466357</v>
       </c>
     </row>
     <row r="232">
@@ -3556,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.400197527989879</v>
       </c>
     </row>
     <row r="233">
@@ -3567,7 +3561,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.354002871520935</v>
+        <v>-0.49314328977379</v>
       </c>
     </row>
     <row r="234">
@@ -3578,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.275126047769745</v>
+        <v>-0.366652500640245</v>
       </c>
     </row>
     <row r="235">
@@ -3589,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.309607583340744</v>
+        <v>-0.301013959385859</v>
       </c>
     </row>
     <row r="236">
@@ -3600,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.301514164671892</v>
+        <v>-0.339477615564619</v>
       </c>
     </row>
     <row r="237">
@@ -3611,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.503904603511002</v>
+        <v>-1.42497483294399</v>
       </c>
     </row>
     <row r="238">
@@ -3622,7 +3616,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.361596663834203</v>
+        <v>0.477668774877418</v>
       </c>
     </row>
     <row r="239">
@@ -3633,7 +3627,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.153895416956653</v>
       </c>
     </row>
     <row r="240">
@@ -3644,7 +3638,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.122304113016966</v>
+        <v>-0.315886086767983</v>
       </c>
     </row>
     <row r="241">
@@ -3655,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-1.6514553942378</v>
+        <v>-0.374542082226742</v>
       </c>
     </row>
     <row r="242">
@@ -3666,7 +3660,7 @@
         <v>16</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.953065239856963</v>
       </c>
     </row>
     <row r="243">
@@ -3677,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.16052285146661</v>
       </c>
     </row>
     <row r="244">
@@ -3688,7 +3682,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.460288363784078</v>
+        <v>-1.05089494986057</v>
       </c>
     </row>
     <row r="245">
@@ -3699,7 +3693,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.825797045801214</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="246">
@@ -3721,7 +3715,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.235513980827369</v>
       </c>
     </row>
     <row r="248">
@@ -3732,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.169597906626163</v>
       </c>
     </row>
     <row r="249">
@@ -3743,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>0.00878674316212247</v>
+        <v>-0.477182706507106</v>
       </c>
     </row>
     <row r="250">
@@ -3754,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.408044629450871</v>
       </c>
     </row>
     <row r="251">
@@ -3776,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>-1.28010224336107</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="253">
@@ -3787,7 +3781,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>0.233099669035628</v>
+        <v>-0.771950977793594</v>
       </c>
     </row>
     <row r="254">
@@ -3798,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.182738175790738</v>
+        <v>-0.177348476410634</v>
       </c>
     </row>
     <row r="255">
@@ -3809,7 +3803,7 @@
         <v>16</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.233943104165664</v>
+        <v>-0.163890698060562</v>
       </c>
     </row>
     <row r="256">
@@ -3820,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.726970574410165</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="257">
@@ -3842,7 +3836,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.207630139095736</v>
+        <v>-2.33328886836378</v>
       </c>
     </row>
     <row r="259">
@@ -3853,7 +3847,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.167611015829292</v>
+        <v>-0.162529429709816</v>
       </c>
     </row>
     <row r="260">
@@ -3864,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-1.32635397938738</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="261">
@@ -3875,7 +3869,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.334685697731735</v>
+        <v>-0.341359428893795</v>
       </c>
     </row>
     <row r="262">
@@ -3919,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.330600726302802</v>
+        <v>-0.494723094203579</v>
       </c>
     </row>
     <row r="266">
@@ -3930,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>0.308776610961666</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="267">
@@ -3941,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.342695724813708</v>
       </c>
     </row>
     <row r="268">
@@ -3952,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.0225545924584207</v>
+        <v>-0.489302392491771</v>
       </c>
     </row>
     <row r="269">
@@ -3963,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.293454418315424</v>
+        <v>-0.338579434660777</v>
       </c>
     </row>
     <row r="270">
@@ -3985,7 +3979,7 @@
         <v>16</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.388873500064917</v>
+        <v>-0.201051607568981</v>
       </c>
     </row>
     <row r="272">
@@ -3996,7 +3990,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.268481691443422</v>
       </c>
     </row>
     <row r="273">
@@ -4018,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.986595094694128</v>
+        <v>-0.762072574242022</v>
       </c>
     </row>
     <row r="275">
@@ -4029,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.637348017355826</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="276">
@@ -4040,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.191233741602496</v>
+        <v>-17.2822592339562</v>
       </c>
     </row>
     <row r="277">
@@ -4084,7 +4078,7 @@
         <v>16</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.315179728659997</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="281">
@@ -4095,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>-1.4509598715482</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="282">
@@ -4106,7 +4100,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.207526145980121</v>
+        <v>-2.25929000566012</v>
       </c>
     </row>
     <row r="283">
@@ -4139,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.551835632140956</v>
       </c>
     </row>
     <row r="286">
@@ -4150,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.353385352967122</v>
+        <v>-0.275258808981095</v>
       </c>
     </row>
     <row r="287">
@@ -4161,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.156116947890335</v>
+        <v>-0.147913588191219</v>
       </c>
     </row>
     <row r="288">
@@ -4183,7 +4177,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.0809485789519158</v>
       </c>
     </row>
     <row r="290">
@@ -4194,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.157974770708464</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="291">
@@ -4216,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.435562546469117</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="293">
@@ -4249,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.205911768138348</v>
+        <v>-0.2181656043059</v>
       </c>
     </row>
     <row r="296">
@@ -4260,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.90278724055684</v>
+        <v>-0.292161556227405</v>
       </c>
     </row>
     <row r="297">
@@ -4293,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.373799772692315</v>
+        <v>-1.14695348609714</v>
       </c>
     </row>
     <row r="300">
@@ -4304,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.578948579910726</v>
+        <v>-0.546233599045935</v>
       </c>
     </row>
     <row r="301">
@@ -4315,7 +4309,7 @@
         <v>16</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.526415980024227</v>
+        <v>-0.933440088467036</v>
       </c>
     </row>
     <row r="302">
@@ -4326,7 +4320,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.33222520521387</v>
       </c>
     </row>
     <row r="303">
@@ -4337,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.389910332666075</v>
+        <v>-0.630685952892988</v>
       </c>
     </row>
     <row r="304">
@@ -4348,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.226828746857266</v>
+        <v>-0.847946003057183</v>
       </c>
     </row>
     <row r="305">
@@ -4359,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.652578411396108</v>
+        <v>-0.225667809218794</v>
       </c>
     </row>
     <row r="306">
@@ -4370,7 +4364,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.25036070226359</v>
+        <v>-0.271636874415208</v>
       </c>
     </row>
     <row r="307">
@@ -4381,7 +4375,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.509211244791046</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="308">
@@ -4392,7 +4386,7 @@
         <v>16</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.374519210485663</v>
       </c>
     </row>
     <row r="309">
@@ -4403,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.06240473206451</v>
       </c>
     </row>
     <row r="310">
@@ -4436,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.712647307599252</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="313">
@@ -4447,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.278386795194878</v>
       </c>
     </row>
     <row r="314">
@@ -4458,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.611814050061829</v>
       </c>
     </row>
     <row r="315">
@@ -4469,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.345820720158768</v>
+        <v>-0.17149422377515</v>
       </c>
     </row>
     <row r="316">
@@ -4480,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.210559197893957</v>
       </c>
     </row>
     <row r="317">
@@ -4502,7 +4496,7 @@
         <v>16</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.363545770844617</v>
+        <v>-0.238115080705722</v>
       </c>
     </row>
     <row r="319">
@@ -4513,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-1.04863020608578</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="320">
@@ -4524,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.231905249638225</v>
       </c>
     </row>
     <row r="321">
@@ -4535,7 +4529,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.386298779004175</v>
       </c>
     </row>
     <row r="322">
@@ -4546,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.187312935477702</v>
+        <v>-0.248055455653118</v>
       </c>
     </row>
     <row r="323">
@@ -4557,7 +4551,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.331272789229913</v>
       </c>
     </row>
     <row r="324">
@@ -4568,7 +4562,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.205149005196979</v>
+        <v>-0.241391964083421</v>
       </c>
     </row>
     <row r="325">
@@ -4579,7 +4573,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.15849286353024</v>
       </c>
     </row>
     <row r="326">
@@ -4590,7 +4584,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.199111507974532</v>
+        <v>-0.208750551094891</v>
       </c>
     </row>
     <row r="327">
@@ -4601,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.571755680913564</v>
+        <v>-0.318436260016122</v>
       </c>
     </row>
     <row r="328">
@@ -4612,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>0.0111458638001499</v>
+        <v>-0.599945952654771</v>
       </c>
     </row>
     <row r="329">
@@ -4656,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-9.55972151500832</v>
+        <v>-0.510512506928329</v>
       </c>
     </row>
     <row r="333">
@@ -4678,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.96742787695207</v>
       </c>
     </row>
     <row r="335">
@@ -4711,7 +4705,7 @@
         <v>16</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.147959183673469</v>
+        <v>-8.3390787723235</v>
       </c>
     </row>
     <row r="338">
@@ -4722,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.219556544681887</v>
       </c>
     </row>
     <row r="339">
@@ -4733,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.25101826468324</v>
+        <v>-0.191516534673876</v>
       </c>
     </row>
     <row r="340">
@@ -4744,7 +4738,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.185429970031928</v>
+        <v>-0.447262075415843</v>
       </c>
     </row>
     <row r="341">
@@ -4755,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.3227970161053</v>
+        <v>-0.328039966908209</v>
       </c>
     </row>
     <row r="342">
@@ -4777,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.364854294568904</v>
+        <v>-0.261453560077635</v>
       </c>
     </row>
     <row r="344">
@@ -4788,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>-0.248507126795742</v>
+        <v>-0.227086394339847</v>
       </c>
     </row>
     <row r="345">
@@ -4799,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.259922317349855</v>
+        <v>-0.189006954168581</v>
       </c>
     </row>
     <row r="346">
@@ -4810,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.379823808477135</v>
+        <v>-0.240471876178804</v>
       </c>
     </row>
     <row r="347">
@@ -4832,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.17532655033015</v>
       </c>
     </row>
     <row r="349">
@@ -4843,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.294325951112009</v>
       </c>
     </row>
     <row r="350">
@@ -4865,7 +4859,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.53295681630445</v>
+        <v>-0.792847849431624</v>
       </c>
     </row>
     <row r="352">
@@ -4876,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>0.12003984455624</v>
+        <v>-0.0270105164271561</v>
       </c>
     </row>
     <row r="353">
@@ -4887,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-1.62828332373504</v>
+        <v>-0.157950407243534</v>
       </c>
     </row>
     <row r="354">
@@ -4898,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.562925837363815</v>
+        <v>-0.168895380091325</v>
       </c>
     </row>
     <row r="355">
@@ -4909,7 +4903,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.92911623632885</v>
       </c>
     </row>
     <row r="356">
@@ -4920,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-2.2321697488395</v>
+        <v>-0.702012918050374</v>
       </c>
     </row>
     <row r="357">
@@ -4931,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.376125058134028</v>
+        <v>-3.63134037049149</v>
       </c>
     </row>
     <row r="358">
@@ -4942,7 +4936,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.536380466118989</v>
       </c>
     </row>
     <row r="359">
@@ -4964,7 +4958,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.0833990370620576</v>
+        <v>0.00612903541522358</v>
       </c>
     </row>
     <row r="361">
@@ -4975,7 +4969,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.191161541948092</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="362">
@@ -4997,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.378023878945021</v>
+        <v>-0.20247820622266</v>
       </c>
     </row>
     <row r="364">
@@ -5008,7 +5002,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.402037174120516</v>
+        <v>-0.402324535868761</v>
       </c>
     </row>
     <row r="365">
@@ -5019,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.162433539946911</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="366">
@@ -5052,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>0.000568258818521961</v>
+        <v>-0.43211320978767</v>
       </c>
     </row>
     <row r="369">
@@ -5063,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-5.33923781484532</v>
+        <v>-0.247898154481079</v>
       </c>
     </row>
     <row r="370">
@@ -5074,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.252507727616171</v>
+        <v>-0.331058151627037</v>
       </c>
     </row>
     <row r="371">
@@ -5085,7 +5079,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.174152236548123</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="372">
@@ -5096,7 +5090,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.903649156105745</v>
       </c>
     </row>
     <row r="373">
@@ -5118,7 +5112,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.03404214800983</v>
       </c>
     </row>
     <row r="375">
@@ -5129,7 +5123,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>0.114424613802219</v>
+        <v>0.0341369540758456</v>
       </c>
     </row>
     <row r="376">
@@ -5173,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.419680730698066</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="380">
@@ -5184,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-1.12443935221349</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="381">
@@ -5195,7 +5189,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.228042967891327</v>
+        <v>-0.302037122388162</v>
       </c>
     </row>
     <row r="382">
@@ -5206,7 +5200,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-3.11487293643974</v>
+        <v>-0.13384950819944</v>
       </c>
     </row>
     <row r="383">
@@ -5217,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.29701325711964</v>
+        <v>-0.335067408521933</v>
       </c>
     </row>
     <row r="384">
@@ -5228,7 +5222,7 @@
         <v>16</v>
       </c>
       <c r="C384" t="n">
-        <v>-1.0149735568935</v>
+        <v>-0.193951976848333</v>
       </c>
     </row>
     <row r="385">
@@ -5250,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.679671989998449</v>
+        <v>-5.32185572363555</v>
       </c>
     </row>
     <row r="387">
@@ -5261,7 +5255,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.172987330679047</v>
+        <v>-0.210365878658512</v>
       </c>
     </row>
     <row r="388">
@@ -5283,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.225114624046958</v>
+        <v>-1.57857432472039</v>
       </c>
     </row>
     <row r="390">
@@ -5294,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.3070761106124</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="391">
@@ -5305,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>0.172545218982801</v>
+        <v>0.120234944072237</v>
       </c>
     </row>
     <row r="392">
@@ -5316,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.443040182393666</v>
+        <v>-0.357721972302845</v>
       </c>
     </row>
     <row r="393">
@@ -5338,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.300794419088308</v>
+        <v>-0.839394836133832</v>
       </c>
     </row>
     <row r="395">
@@ -5349,7 +5343,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>0.240036969057144</v>
+        <v>-0.0327154795112046</v>
       </c>
     </row>
     <row r="396">
@@ -5360,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.264575117672058</v>
+        <v>-0.310197866998397</v>
       </c>
     </row>
     <row r="397">
@@ -5382,7 +5376,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-1.10610611452128</v>
+        <v>-0.349214306708175</v>
       </c>
     </row>
     <row r="399">
@@ -5393,7 +5387,7 @@
         <v>16</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.111859643328526</v>
+        <v>-0.744328426199254</v>
       </c>
     </row>
     <row r="400">
@@ -5404,7 +5398,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.177922538615695</v>
+        <v>-1.13911439458358</v>
       </c>
     </row>
     <row r="401">
@@ -5415,7 +5409,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.951256962487503</v>
       </c>
     </row>
     <row r="402">
@@ -5437,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-5.46570516104242</v>
+        <v>-0.11074095938784</v>
       </c>
     </row>
     <row r="404">
@@ -5448,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.158086835626267</v>
+        <v>-0.138615351413632</v>
       </c>
     </row>
     <row r="405">
@@ -5459,7 +5453,7 @@
         <v>16</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.60664777468265</v>
       </c>
     </row>
     <row r="406">
@@ -5470,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.157940152659572</v>
       </c>
     </row>
     <row r="407">
@@ -5481,7 +5475,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.510622399312363</v>
+        <v>-1.24568273615709</v>
       </c>
     </row>
     <row r="408">
@@ -5492,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.183479075901108</v>
+        <v>-0.427624172488518</v>
       </c>
     </row>
     <row r="409">
@@ -5503,7 +5497,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-1.72414039229824</v>
+        <v>-1.74013988091726</v>
       </c>
     </row>
     <row r="410">
@@ -5525,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.61828137159342</v>
+        <v>-0.486430812731731</v>
       </c>
     </row>
     <row r="412">
@@ -5547,7 +5541,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>0.0725675613109211</v>
+        <v>-0.892337994260073</v>
       </c>
     </row>
     <row r="414">
@@ -5558,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.171831742898483</v>
+        <v>0.103280149445549</v>
       </c>
     </row>
     <row r="415">
@@ -5569,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.863354606755752</v>
+        <v>-0.233952779870258</v>
       </c>
     </row>
     <row r="416">
@@ -5580,7 +5574,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.339047017904206</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="417">
@@ -5591,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.276177106522858</v>
       </c>
     </row>
     <row r="418">
@@ -5602,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.159965694674971</v>
+        <v>-0.171973666899084</v>
       </c>
     </row>
     <row r="419">
@@ -5613,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.281991820976903</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="420">
@@ -5624,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-1.12187515901018</v>
+        <v>-0.190621472251564</v>
       </c>
     </row>
     <row r="421">
@@ -5657,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.333105054902049</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="424">
@@ -5679,7 +5673,7 @@
         <v>16</v>
       </c>
       <c r="C425" t="n">
-        <v>-0.147959183673469</v>
+        <v>-57.3016050226802</v>
       </c>
     </row>
     <row r="426">
@@ -5712,7 +5706,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.455722864500771</v>
+        <v>-0.16215442805498</v>
       </c>
     </row>
     <row r="429">
@@ -5723,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.534401306835203</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="430">
@@ -5745,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.399300212055062</v>
+        <v>-1.1918694144894</v>
       </c>
     </row>
     <row r="432">
@@ -5756,7 +5750,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.494868415259598</v>
+        <v>-0.349840454403485</v>
       </c>
     </row>
     <row r="433">
@@ -5767,7 +5761,7 @@
         <v>16</v>
       </c>
       <c r="C433" t="n">
-        <v>-0.397575317267337</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="434">
@@ -5789,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.248079665303376</v>
+        <v>-0.274477801420297</v>
       </c>
     </row>
     <row r="436">
@@ -5800,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.213254831511618</v>
+        <v>-0.294754513960384</v>
       </c>
     </row>
     <row r="437">
@@ -5811,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.234322691806607</v>
+        <v>-0.340468467864045</v>
       </c>
     </row>
     <row r="438">
@@ -5822,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.494154929282291</v>
+        <v>-0.0852476338597252</v>
       </c>
     </row>
     <row r="439">
@@ -5833,7 +5827,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.195835379377315</v>
       </c>
     </row>
     <row r="440">
@@ -5844,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.244896447590946</v>
+        <v>-0.223930968077774</v>
       </c>
     </row>
     <row r="441">
@@ -5855,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.981127749375446</v>
+        <v>-0.750985953677433</v>
       </c>
     </row>
     <row r="442">
@@ -5877,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.906173926054536</v>
       </c>
     </row>
     <row r="444">
@@ -5888,7 +5882,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.131909412675674</v>
+        <v>-0.142493165114127</v>
       </c>
     </row>
     <row r="445">
@@ -5910,7 +5904,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.43884438642398</v>
       </c>
     </row>
     <row r="447">
@@ -5921,7 +5915,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.266694358799499</v>
       </c>
     </row>
     <row r="448">
@@ -5932,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.442730432477951</v>
+        <v>-0.0838227258714541</v>
       </c>
     </row>
     <row r="449">
@@ -5943,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.350702745298508</v>
+        <v>-2.79003126225221</v>
       </c>
     </row>
     <row r="450">
@@ -5954,7 +5948,7 @@
         <v>16</v>
       </c>
       <c r="C450" t="n">
-        <v>-0.915744410729153</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="451">
@@ -5987,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>0.103888096512178</v>
+        <v>-0.371292533621314</v>
       </c>
     </row>
     <row r="454">
@@ -5998,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.180772183392277</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="455">
@@ -6009,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.271778937360688</v>
+        <v>-0.202170618179861</v>
       </c>
     </row>
     <row r="456">
@@ -6020,7 +6014,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.377430528554847</v>
       </c>
     </row>
     <row r="457">
@@ -6042,7 +6036,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-1.41345655118527</v>
+        <v>-0.174119176995912</v>
       </c>
     </row>
     <row r="459">
@@ -6053,7 +6047,7 @@
         <v>16</v>
       </c>
       <c r="C459" t="n">
-        <v>-1.80694712165199</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="460">
@@ -6119,7 +6113,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.197255727382909</v>
+        <v>-0.492781674106802</v>
       </c>
     </row>
     <row r="466">
@@ -6130,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.247532651567236</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="467">
@@ -6152,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>0.294628928080821</v>
+        <v>-3.17218669671594</v>
       </c>
     </row>
     <row r="469">
@@ -6163,7 +6157,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.406059704294848</v>
+        <v>-0.265287953486357</v>
       </c>
     </row>
     <row r="470">
@@ -6185,7 +6179,7 @@
         <v>16</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.592911391080118</v>
+        <v>-0.137173493991569</v>
       </c>
     </row>
     <row r="472">
@@ -6196,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.255835953236666</v>
+        <v>-0.97707291202328</v>
       </c>
     </row>
     <row r="473">
@@ -6218,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.784131672643471</v>
+        <v>-0.387437370157957</v>
       </c>
     </row>
     <row r="475">
@@ -6240,7 +6234,7 @@
         <v>16</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.147959183673469</v>
+        <v>-13.3666707903282</v>
       </c>
     </row>
     <row r="477">
@@ -6251,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.501267378774295</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="478">
@@ -6262,7 +6256,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.175385557712239</v>
+        <v>-0.173016686987693</v>
       </c>
     </row>
     <row r="479">
@@ -6273,7 +6267,7 @@
         <v>16</v>
       </c>
       <c r="C479" t="n">
-        <v>-0.311155853808512</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="480">
@@ -6284,7 +6278,7 @@
         <v>16</v>
       </c>
       <c r="C480" t="n">
-        <v>-0.317655222470601</v>
+        <v>-0.0998618313467841</v>
       </c>
     </row>
     <row r="481">
@@ -6295,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>-0.385131035000021</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="482">
@@ -6317,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.272788473131576</v>
       </c>
     </row>
     <row r="484">
@@ -6339,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.176143117349261</v>
       </c>
     </row>
     <row r="486">
@@ -6361,7 +6355,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.224804629858155</v>
+        <v>-0.316661793384887</v>
       </c>
     </row>
     <row r="488">
@@ -6383,7 +6377,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.985649652623081</v>
       </c>
     </row>
     <row r="490">
@@ -6394,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-1.4727709046955</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="491">
@@ -6427,7 +6421,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.32932634108895</v>
       </c>
     </row>
     <row r="494">
@@ -6449,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.214635752032912</v>
+        <v>-0.228413599637601</v>
       </c>
     </row>
     <row r="496">
@@ -6460,7 +6454,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="n">
-        <v>0.511972405243637</v>
+        <v>-0.101864625565134</v>
       </c>
     </row>
     <row r="497">
@@ -6493,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-1.87829853939462</v>
+        <v>0.160952397856412</v>
       </c>
     </row>
     <row r="500">
@@ -6504,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.580329522827815</v>
+        <v>-0.814938510495669</v>
       </c>
     </row>
     <row r="501">
@@ -6526,7 +6520,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="n">
-        <v>-1.22106941075976</v>
+        <v>-2.87528162401861</v>
       </c>
     </row>
     <row r="503">
@@ -6537,7 +6531,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.254990440860877</v>
+        <v>-0.48142480600927</v>
       </c>
     </row>
     <row r="504">
@@ -6548,7 +6542,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.192768594038299</v>
+        <v>-2.22653749458371</v>
       </c>
     </row>
     <row r="505">
@@ -6559,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="C505" t="n">
-        <v>-1.18806987048854</v>
+        <v>-0.440424499350893</v>
       </c>
     </row>
     <row r="506">
@@ -6570,7 +6564,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.165375956019809</v>
       </c>
     </row>
     <row r="507">
@@ -6592,7 +6586,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.242828327109629</v>
+        <v>-0.216082779423879</v>
       </c>
     </row>
     <row r="509">
@@ -6603,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.19203472378408</v>
+        <v>-0.265552732609647</v>
       </c>
     </row>
     <row r="510">
@@ -6614,7 +6608,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.147959183673469</v>
+        <v>-18.7232917735645</v>
       </c>
     </row>
     <row r="511">
@@ -6625,7 +6619,7 @@
         <v>16</v>
       </c>
       <c r="C511" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.672376834082277</v>
       </c>
     </row>
     <row r="512">
@@ -6647,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.99783903447349</v>
       </c>
     </row>
     <row r="514">
@@ -6669,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.177276364144965</v>
       </c>
     </row>
     <row r="516">
@@ -6702,7 +6696,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.206215617327258</v>
+        <v>-0.171832547050088</v>
       </c>
     </row>
     <row r="519">
@@ -6713,7 +6707,7 @@
         <v>16</v>
       </c>
       <c r="C519" t="n">
-        <v>-1.48221798188434</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="520">
@@ -6724,7 +6718,7 @@
         <v>16</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.25473046990452</v>
       </c>
     </row>
     <row r="521">
@@ -6735,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.249695565153179</v>
       </c>
     </row>
     <row r="522">
@@ -6746,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.200521320899781</v>
       </c>
     </row>
     <row r="523">
@@ -6768,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.254200010814312</v>
+        <v>-0.284339785155167</v>
       </c>
     </row>
     <row r="525">
@@ -6779,7 +6773,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.176505450498626</v>
+        <v>-0.203000343761966</v>
       </c>
     </row>
     <row r="526">
@@ -6801,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.87373633279982</v>
       </c>
     </row>
     <row r="528">
@@ -6812,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.0922462417041712</v>
+        <v>-0.206007965098721</v>
       </c>
     </row>
     <row r="529">
@@ -6856,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.429254732783691</v>
+        <v>-0.621863342355621</v>
       </c>
     </row>
     <row r="533">
@@ -6911,7 +6905,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.185363194969977</v>
+        <v>-0.171162091970332</v>
       </c>
     </row>
     <row r="538">
@@ -6922,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.142822329200623</v>
       </c>
     </row>
     <row r="539">
@@ -6944,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-1.34015368633186</v>
+        <v>-0.422443520527573</v>
       </c>
     </row>
     <row r="541">
@@ -6955,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.767226381128776</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="542">
@@ -6977,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.298067328046947</v>
+        <v>-0.186182073313464</v>
       </c>
     </row>
     <row r="544">
@@ -6999,7 +6993,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.308783974171124</v>
+        <v>-0.392962317171573</v>
       </c>
     </row>
     <row r="546">
@@ -7010,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>0.0675269550561973</v>
+        <v>0.255602362646964</v>
       </c>
     </row>
     <row r="547">
@@ -7032,7 +7026,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.314871259136471</v>
       </c>
     </row>
     <row r="549">
@@ -7043,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.247830429702125</v>
+        <v>-1.24422583070944</v>
       </c>
     </row>
     <row r="550">
@@ -7065,7 +7059,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-3.50175292666448</v>
+        <v>-5.02005651630499</v>
       </c>
     </row>
     <row r="552">
@@ -7076,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.196702655621253</v>
+        <v>-0.163115982383953</v>
       </c>
     </row>
     <row r="553">
@@ -7087,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.148171081307544</v>
+        <v>-0.14080898328816</v>
       </c>
     </row>
     <row r="554">
@@ -7098,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.111063491708576</v>
+        <v>-0.152800705288719</v>
       </c>
     </row>
     <row r="555">
@@ -7120,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.381692959657875</v>
+        <v>-0.984544767396342</v>
       </c>
     </row>
     <row r="557">
@@ -7131,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.206611753142838</v>
+        <v>-0.15288768559803</v>
       </c>
     </row>
     <row r="558">
@@ -7164,7 +7158,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.110037719655342</v>
+        <v>-0.093884251179426</v>
       </c>
     </row>
     <row r="561">
@@ -7197,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.372961084602944</v>
+        <v>-0.230502064701136</v>
       </c>
     </row>
     <row r="564">
@@ -7208,7 +7202,7 @@
         <v>16</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.537447695215059</v>
+        <v>-0.352136896482729</v>
       </c>
     </row>
     <row r="565">
@@ -7241,7 +7235,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-1.64473494379719</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="568">
@@ -7252,7 +7246,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.194699855828129</v>
+        <v>-0.348844009759252</v>
       </c>
     </row>
     <row r="569">
@@ -7263,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-5.33518329542122</v>
+        <v>-0.15468011132144</v>
       </c>
     </row>
     <row r="570">
@@ -7274,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.271593470235514</v>
+        <v>-0.526730601517396</v>
       </c>
     </row>
     <row r="571">
@@ -7296,7 +7290,7 @@
         <v>16</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.543763275007708</v>
+        <v>-2.01008654788434</v>
       </c>
     </row>
     <row r="573">
@@ -7318,7 +7312,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.311571898724094</v>
       </c>
     </row>
     <row r="575">
@@ -7329,7 +7323,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.173639332145107</v>
+        <v>-0.17218083489901</v>
       </c>
     </row>
     <row r="576">
@@ -7340,7 +7334,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-5.43128084830784</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="577">
@@ -7384,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-1.20524160907033</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="581">
@@ -7395,7 +7389,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.205218416440907</v>
+        <v>-1.27598338447954</v>
       </c>
     </row>
     <row r="582">
@@ -7406,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>0.0064349956065195</v>
+        <v>-1.82948314344725</v>
       </c>
     </row>
     <row r="583">
@@ -7417,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.270540340964253</v>
+        <v>-0.31523689763168</v>
       </c>
     </row>
     <row r="584">
@@ -7428,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.321969800012625</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="585">
@@ -7439,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.201376209201476</v>
       </c>
     </row>
     <row r="586">
@@ -7450,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-1.63116318999383</v>
+        <v>-4.30362015674281</v>
       </c>
     </row>
     <row r="587">
@@ -7461,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.188957749906636</v>
+        <v>-0.279744886315086</v>
       </c>
     </row>
     <row r="588">
@@ -7472,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.22492077327721</v>
+        <v>-0.234378411554315</v>
       </c>
     </row>
     <row r="589">
@@ -7483,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.294300479717519</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="590">
@@ -7494,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.238448549032612</v>
+        <v>-1.81763643772331</v>
       </c>
     </row>
     <row r="591">
@@ -7505,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>0.10174330602776</v>
+        <v>0.198359593441682</v>
       </c>
     </row>
     <row r="592">
@@ -7516,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.358341340164403</v>
       </c>
     </row>
     <row r="593">
@@ -7538,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>0.120238707939663</v>
+        <v>-0.223220627870178</v>
       </c>
     </row>
     <row r="595">
@@ -7549,7 +7543,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.228760768146887</v>
+        <v>-0.166053068021274</v>
       </c>
     </row>
     <row r="596">
@@ -7560,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.399619420198828</v>
+        <v>-0.167296341390273</v>
       </c>
     </row>
     <row r="597">
@@ -7571,7 +7565,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-4.58175824690831</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="598">
@@ -7582,7 +7576,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>0.02289909557347</v>
+        <v>-0.353159026215159</v>
       </c>
     </row>
     <row r="599">
@@ -7593,7 +7587,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.163987727834492</v>
+        <v>-0.029591819419106</v>
       </c>
     </row>
     <row r="600">
@@ -7604,7 +7598,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.545805820812481</v>
       </c>
     </row>
     <row r="601">
@@ -7615,7 +7609,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.23069990936954</v>
+        <v>-0.158182171444626</v>
       </c>
     </row>
     <row r="602">
@@ -7626,7 +7620,7 @@
         <v>16</v>
       </c>
       <c r="C602" t="n">
-        <v>-0.53220030772238</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="603">
@@ -7637,7 +7631,7 @@
         <v>16</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.04081992513965</v>
       </c>
     </row>
     <row r="604">
@@ -7670,7 +7664,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.184900435263901</v>
+        <v>-0.228517726171041</v>
       </c>
     </row>
     <row r="607">
@@ -7681,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.166651637971331</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="608">
@@ -7692,7 +7686,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.90705464903363</v>
       </c>
     </row>
     <row r="609">
@@ -7703,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.627767484915022</v>
+        <v>-0.510815299701289</v>
       </c>
     </row>
     <row r="610">
@@ -7725,7 +7719,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.298329351176065</v>
       </c>
     </row>
     <row r="612">
@@ -7747,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.412675336860965</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="614">
@@ -7758,7 +7752,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.449354660639454</v>
+        <v>-0.26282964197311</v>
       </c>
     </row>
     <row r="615">
@@ -7769,7 +7763,7 @@
         <v>16</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.529689552720628</v>
+        <v>-0.793455248316774</v>
       </c>
     </row>
     <row r="616">
@@ -7780,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>0.576003823183088</v>
+        <v>0.628005799817098</v>
       </c>
     </row>
     <row r="617">
@@ -7802,7 +7796,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.240435747047582</v>
+        <v>-0.226535201924853</v>
       </c>
     </row>
     <row r="619">
@@ -7813,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>0.424161292060314</v>
+        <v>-0.472572798639611</v>
       </c>
     </row>
     <row r="620">
@@ -7824,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>0.5062837006561</v>
+        <v>-0.165241763821166</v>
       </c>
     </row>
     <row r="621">
@@ -7846,7 +7840,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.80263495864593</v>
       </c>
     </row>
     <row r="623">
@@ -7857,7 +7851,7 @@
         <v>16</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.245836396358917</v>
+        <v>-0.24726480771816</v>
       </c>
     </row>
     <row r="624">
@@ -7868,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.62591474673449</v>
+        <v>-0.412036638213895</v>
       </c>
     </row>
     <row r="625">
@@ -7923,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.363014712378366</v>
+        <v>-0.24964755319894</v>
       </c>
     </row>
     <row r="630">
@@ -7945,7 +7939,7 @@
         <v>16</v>
       </c>
       <c r="C631" t="n">
-        <v>-1.76370295114654</v>
+        <v>-0.135555699692263</v>
       </c>
     </row>
     <row r="632">
@@ -7967,7 +7961,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.214699589045479</v>
+        <v>-0.156754125663453</v>
       </c>
     </row>
     <row r="634">
@@ -7978,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.47164793029474</v>
       </c>
     </row>
     <row r="635">
@@ -7989,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.162969095080098</v>
       </c>
     </row>
     <row r="636">
@@ -8000,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.266683719203479</v>
+        <v>-0.19758635302628</v>
       </c>
     </row>
     <row r="637">
@@ -8011,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.485143090748334</v>
+        <v>-0.379877762118224</v>
       </c>
     </row>
     <row r="638">
@@ -8022,7 +8016,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.446097442723559</v>
+        <v>-0.348198023060563</v>
       </c>
     </row>
     <row r="639">
@@ -8044,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.151287862537032</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="641">
@@ -8066,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.30237891376306</v>
+        <v>0.0611929948809569</v>
       </c>
     </row>
     <row r="643">
@@ -8110,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.206725240121633</v>
+        <v>-2.15752966938575</v>
       </c>
     </row>
     <row r="647">
@@ -8121,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.543854410130988</v>
+        <v>-8.82159597739398</v>
       </c>
     </row>
     <row r="648">
@@ -8132,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.394642021842171</v>
+        <v>-0.171765347082184</v>
       </c>
     </row>
     <row r="649">
@@ -8143,7 +8137,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-1.23239466957183</v>
+        <v>-1.50717609447932</v>
       </c>
     </row>
     <row r="650">
@@ -8154,7 +8148,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.222450694286928</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="651">
@@ -8165,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.201044765358948</v>
       </c>
     </row>
     <row r="652">
@@ -8209,7 +8203,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.239459869940313</v>
+        <v>-0.259261866293591</v>
       </c>
     </row>
     <row r="656">
@@ -8220,7 +8214,7 @@
         <v>16</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.314239640635169</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="657">
@@ -8253,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.635796790095895</v>
       </c>
     </row>
     <row r="660">
@@ -8264,7 +8258,7 @@
         <v>16</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.153048217447184</v>
+        <v>-0.104374605226754</v>
       </c>
     </row>
     <row r="661">
@@ -8275,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-1.21581938615734</v>
+        <v>-0.422255933385583</v>
       </c>
     </row>
     <row r="662">
@@ -8297,7 +8291,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-1.84918265528312</v>
+        <v>-1.46488723946898</v>
       </c>
     </row>
     <row r="664">
@@ -8308,7 +8302,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.270793488363793</v>
       </c>
     </row>
     <row r="665">
@@ -8363,7 +8357,7 @@
         <v>16</v>
       </c>
       <c r="C669" t="n">
-        <v>-2.05371424776377</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="670">
@@ -8374,7 +8368,7 @@
         <v>16</v>
       </c>
       <c r="C670" t="n">
-        <v>0.439470432470844</v>
+        <v>-0.00672103740820651</v>
       </c>
     </row>
     <row r="671">
@@ -8396,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.386989983954209</v>
+        <v>-0.346144145401885</v>
       </c>
     </row>
     <row r="673">
@@ -8407,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.920489385747371</v>
       </c>
     </row>
     <row r="674">
@@ -8418,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-1.07608870328874</v>
+        <v>-0.164893235262427</v>
       </c>
     </row>
     <row r="675">
@@ -8429,7 +8423,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.176823044253987</v>
       </c>
     </row>
     <row r="676">
@@ -8440,7 +8434,7 @@
         <v>16</v>
       </c>
       <c r="C676" t="n">
-        <v>0.336725462677763</v>
+        <v>0.118080446183789</v>
       </c>
     </row>
     <row r="677">
@@ -8451,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.16112099818687</v>
+        <v>-0.0907999924050251</v>
       </c>
     </row>
     <row r="678">
@@ -8462,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.269898319576941</v>
+        <v>-0.446767100792892</v>
       </c>
     </row>
     <row r="679">
@@ -8473,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.797217880501446</v>
+        <v>-0.48445464498964</v>
       </c>
     </row>
     <row r="680">
@@ -8484,7 +8478,7 @@
         <v>16</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.261557386544204</v>
+        <v>-0.173779709092592</v>
       </c>
     </row>
     <row r="681">
@@ -8495,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.270829137621184</v>
+        <v>-0.212797788187696</v>
       </c>
     </row>
     <row r="682">
@@ -8506,7 +8500,7 @@
         <v>16</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.165146180019089</v>
+        <v>-0.136030868896299</v>
       </c>
     </row>
     <row r="683">
@@ -8517,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.807238182862292</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="684">
@@ -8528,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>0.266548117787534</v>
+        <v>0.292972615566252</v>
       </c>
     </row>
     <row r="685">
@@ -8572,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.370492430381261</v>
+        <v>-1.69723484525369</v>
       </c>
     </row>
     <row r="689">
@@ -8594,7 +8588,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-1.02445087726722</v>
+        <v>-1.26442722156095</v>
       </c>
     </row>
     <row r="691">
@@ -8605,7 +8599,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.525795701457286</v>
       </c>
     </row>
     <row r="692">
@@ -8616,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.203636558858698</v>
+        <v>-1.50097385191915</v>
       </c>
     </row>
     <row r="693">
@@ -8627,7 +8621,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.263985957082886</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="694">
@@ -8638,7 +8632,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.76088451384368</v>
+        <v>-0.811323368507691</v>
       </c>
     </row>
     <row r="695">
@@ -8649,7 +8643,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.137382839805207</v>
       </c>
     </row>
     <row r="696">
@@ -8660,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.25247602408568</v>
+        <v>-3.26464955320564</v>
       </c>
     </row>
     <row r="697">
@@ -8671,7 +8665,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.238704063536124</v>
       </c>
     </row>
     <row r="698">
@@ -8682,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.214704662386937</v>
+        <v>-0.290433808000008</v>
       </c>
     </row>
     <row r="699">
@@ -8704,7 +8698,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.275796197239676</v>
+        <v>-0.254198444177716</v>
       </c>
     </row>
     <row r="701">
@@ -8715,7 +8709,7 @@
         <v>16</v>
       </c>
       <c r="C701" t="n">
-        <v>-1.22142543936699</v>
+        <v>-0.297228985364594</v>
       </c>
     </row>
     <row r="702">
@@ -8748,7 +8742,7 @@
         <v>16</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.220426402874015</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="705">
@@ -8792,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.188308869291222</v>
+        <v>-0.17404092217916</v>
       </c>
     </row>
     <row r="709">
@@ -8803,7 +8797,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-1.24657659937967</v>
+        <v>-0.401053824707868</v>
       </c>
     </row>
     <row r="710">
@@ -8814,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>0.677284311006326</v>
+        <v>0.542669794831256</v>
       </c>
     </row>
     <row r="711">
@@ -8836,7 +8830,7 @@
         <v>16</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.177252248684853</v>
+        <v>-0.270153016402143</v>
       </c>
     </row>
     <row r="713">
@@ -8847,7 +8841,7 @@
         <v>16</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.172782354017602</v>
       </c>
     </row>
     <row r="714">
@@ -8858,7 +8852,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.0911009337568887</v>
+        <v>-0.173637667697408</v>
       </c>
     </row>
     <row r="715">
@@ -8869,7 +8863,7 @@
         <v>16</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.157188049447274</v>
+        <v>-9.95154964497892</v>
       </c>
     </row>
     <row r="716">
@@ -8880,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>0.252307466615192</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="717">
@@ -8891,7 +8885,7 @@
         <v>16</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.150666150711747</v>
+        <v>-0.154268545368214</v>
       </c>
     </row>
     <row r="718">
@@ -8902,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.221761383069902</v>
+        <v>-0.654251384839323</v>
       </c>
     </row>
     <row r="719">
@@ -8924,7 +8918,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.17493624817209</v>
+        <v>-0.207892877300786</v>
       </c>
     </row>
     <row r="721">
@@ -8946,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>0.207502129166881</v>
+        <v>-0.745021730002882</v>
       </c>
     </row>
     <row r="723">
@@ -8957,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.508239915745854</v>
+        <v>-0.227707957612745</v>
       </c>
     </row>
     <row r="724">
@@ -8979,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.317198968190904</v>
+        <v>-0.214626884446275</v>
       </c>
     </row>
     <row r="726">
@@ -9001,7 +8995,7 @@
         <v>16</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.167079853064839</v>
+        <v>-0.18291265747404</v>
       </c>
     </row>
     <row r="728">
@@ -9012,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>0.0377180545971567</v>
+        <v>-0.107858895763991</v>
       </c>
     </row>
     <row r="729">
@@ -9023,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.299537838615082</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="730">
@@ -9034,7 +9028,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.153626079236646</v>
+        <v>-0.564755139588342</v>
       </c>
     </row>
     <row r="731">
@@ -9056,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.198186895521104</v>
+        <v>-0.677792227268984</v>
       </c>
     </row>
     <row r="733">
@@ -9067,7 +9061,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.151855733267392</v>
+        <v>-0.234431355984308</v>
       </c>
     </row>
     <row r="734">
@@ -9078,7 +9072,7 @@
         <v>16</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.243118448458499</v>
       </c>
     </row>
     <row r="735">
@@ -9100,7 +9094,7 @@
         <v>16</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.185253947355476</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="737">
@@ -9111,7 +9105,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.178879737157938</v>
       </c>
     </row>
     <row r="738">
@@ -9122,7 +9116,7 @@
         <v>16</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.607075783172896</v>
+        <v>-0.803268836707985</v>
       </c>
     </row>
     <row r="739">
@@ -9133,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.150475988621136</v>
+        <v>-0.156782669972918</v>
       </c>
     </row>
     <row r="740">
@@ -9144,7 +9138,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.361137499981842</v>
+        <v>-0.453036513576025</v>
       </c>
     </row>
     <row r="741">
@@ -9155,7 +9149,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.337902305312695</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="742">
@@ -9177,7 +9171,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.2411093391516</v>
       </c>
     </row>
     <row r="744">
@@ -9188,7 +9182,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.515697294960135</v>
+        <v>-7.7676911745529</v>
       </c>
     </row>
     <row r="745">
@@ -9199,7 +9193,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.768269938973973</v>
+        <v>-2.45369496888645</v>
       </c>
     </row>
     <row r="746">
@@ -9221,7 +9215,7 @@
         <v>16</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.321025599208789</v>
+        <v>-0.280078040492235</v>
       </c>
     </row>
     <row r="748">
@@ -9243,7 +9237,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.292544967069698</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="750">
@@ -9254,7 +9248,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-1.3484429424678</v>
+        <v>0.177599652540535</v>
       </c>
     </row>
     <row r="751">
@@ -9276,7 +9270,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.542547907709151</v>
+        <v>-0.327495266869841</v>
       </c>
     </row>
     <row r="753">
@@ -9287,7 +9281,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.600992742536892</v>
+        <v>-0.566563922771771</v>
       </c>
     </row>
     <row r="754">
@@ -9298,7 +9292,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.436437919477264</v>
       </c>
     </row>
     <row r="755">
@@ -9309,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.215030827591015</v>
+        <v>-0.214783057766747</v>
       </c>
     </row>
     <row r="756">
@@ -9320,7 +9314,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.184791296085938</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="757">
@@ -9331,7 +9325,7 @@
         <v>16</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.448254542609641</v>
+        <v>-0.406793564423478</v>
       </c>
     </row>
     <row r="758">
@@ -9342,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.414067463551861</v>
+        <v>-0.177930173701429</v>
       </c>
     </row>
     <row r="759">
@@ -9353,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.14795918367347</v>
+        <v>-9.45642196758806</v>
       </c>
     </row>
     <row r="760">
@@ -9364,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.384454223362275</v>
       </c>
     </row>
     <row r="761">
@@ -9375,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>0.140357279193497</v>
+        <v>-1.0939530987552</v>
       </c>
     </row>
     <row r="762">
@@ -9386,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.314773565800335</v>
+        <v>-0.0858742771490395</v>
       </c>
     </row>
     <row r="763">
@@ -9397,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>0.0555085146629618</v>
+        <v>-0.156584209734721</v>
       </c>
     </row>
     <row r="764">
@@ -9419,7 +9413,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.299519999882015</v>
+        <v>-0.216873950816337</v>
       </c>
     </row>
     <row r="766">
@@ -9430,7 +9424,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.337340615509671</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="767">
@@ -9452,7 +9446,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.753216038527714</v>
+        <v>-1.67195011169375</v>
       </c>
     </row>
     <row r="769">
@@ -9463,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.952118492801879</v>
+        <v>-0.488509739896496</v>
       </c>
     </row>
     <row r="770">
@@ -9485,7 +9479,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.652107296808225</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="772">
@@ -9496,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.245562276542335</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="773">
@@ -9507,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.90875671065142</v>
       </c>
     </row>
     <row r="774">
@@ -9529,7 +9523,7 @@
         <v>16</v>
       </c>
       <c r="C775" t="n">
-        <v>-1.23008150958031</v>
+        <v>-0.291573748212882</v>
       </c>
     </row>
     <row r="776">
@@ -9540,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.13460322089321</v>
+        <v>-0.159793495170069</v>
       </c>
     </row>
     <row r="777">
@@ -9562,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.248764876718852</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="779">
@@ -9573,7 +9567,7 @@
         <v>16</v>
       </c>
       <c r="C779" t="n">
-        <v>-1.06514694341583</v>
+        <v>-0.307619804293119</v>
       </c>
     </row>
     <row r="780">
@@ -9584,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>0.136608288710818</v>
+        <v>-0.190047608515064</v>
       </c>
     </row>
     <row r="781">
@@ -9595,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.147808940958096</v>
+        <v>-0.775817755745922</v>
       </c>
     </row>
     <row r="782">
@@ -9617,7 +9611,7 @@
         <v>16</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.285067087150438</v>
+        <v>-0.763101044525941</v>
       </c>
     </row>
     <row r="784">
@@ -9628,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.0245690493632489</v>
+        <v>-0.138597034869732</v>
       </c>
     </row>
     <row r="785">
@@ -9650,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-1.21061995819694</v>
+        <v>-3.18212407911009</v>
       </c>
     </row>
     <row r="787">
@@ -9683,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.573668324616105</v>
+        <v>-0.226887023423442</v>
       </c>
     </row>
     <row r="790">
@@ -9694,7 +9688,7 @@
         <v>16</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.45605625078324</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="791">
@@ -9716,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.73941955989232</v>
+        <v>-0.394097163809745</v>
       </c>
     </row>
     <row r="793">
@@ -9727,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.299310373312021</v>
+        <v>-0.312877964250034</v>
       </c>
     </row>
     <row r="794">
@@ -9738,7 +9732,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.979943356776493</v>
       </c>
     </row>
     <row r="795">
@@ -9749,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.171315724035344</v>
+        <v>-0.261826178530829</v>
       </c>
     </row>
     <row r="796">
@@ -9771,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>0.0817645808510866</v>
+        <v>0.0749149297404073</v>
       </c>
     </row>
     <row r="798">
@@ -9804,7 +9798,7 @@
         <v>16</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.00464232396331843</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="801">
@@ -9826,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.377752555054858</v>
+        <v>-0.432333912623194</v>
       </c>
     </row>
     <row r="803">
@@ -9837,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.220459932137892</v>
+        <v>-0.247174774258119</v>
       </c>
     </row>
     <row r="804">
@@ -9848,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.667374179503411</v>
       </c>
     </row>
     <row r="805">
@@ -9859,7 +9853,7 @@
         <v>16</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.715105917051183</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="806">
@@ -9870,7 +9864,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.406651827180419</v>
       </c>
     </row>
     <row r="807">
@@ -9881,7 +9875,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.922576467832801</v>
+        <v>-0.0929162825227905</v>
       </c>
     </row>
     <row r="808">
@@ -9892,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.37545648413627</v>
+        <v>-0.384743190398376</v>
       </c>
     </row>
     <row r="809">
@@ -9903,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.345580028201738</v>
+        <v>-0.415667421957713</v>
       </c>
     </row>
     <row r="810">
@@ -9914,7 +9908,7 @@
         <v>16</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.211155959936845</v>
+        <v>-0.195070293354481</v>
       </c>
     </row>
     <row r="811">
@@ -9925,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.756192221869488</v>
+        <v>-0.634450932499035</v>
       </c>
     </row>
     <row r="812">
@@ -9947,7 +9941,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.891026759311234</v>
+        <v>-0.248114648525847</v>
       </c>
     </row>
     <row r="814">
@@ -9958,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.257485910142111</v>
+        <v>-0.418333118007767</v>
       </c>
     </row>
     <row r="815">
@@ -9969,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.842585936817906</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="816">
@@ -9980,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>0.3569581414279</v>
+        <v>-0.250282268948549</v>
       </c>
     </row>
     <row r="817">
@@ -10013,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-1.60198071232423</v>
+        <v>-2.00272555600895</v>
       </c>
     </row>
     <row r="820">
@@ -10024,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.22610441337289</v>
       </c>
     </row>
     <row r="821">
@@ -10035,7 +10029,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.654353986406669</v>
+        <v>-0.101244016876874</v>
       </c>
     </row>
     <row r="822">
@@ -10046,7 +10040,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.173663519427259</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="823">
@@ -10068,7 +10062,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.244244190374693</v>
+        <v>-0.278001212542762</v>
       </c>
     </row>
     <row r="825">
@@ -10079,7 +10073,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.166643484445748</v>
+        <v>-0.178817462014306</v>
       </c>
     </row>
     <row r="826">
@@ -10090,7 +10084,7 @@
         <v>16</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.214250214488532</v>
+        <v>-0.209886771326877</v>
       </c>
     </row>
     <row r="827">
@@ -10101,7 +10095,7 @@
         <v>16</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.192348296630829</v>
+        <v>-0.271113627100565</v>
       </c>
     </row>
     <row r="828">
@@ -10112,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.28221572643256</v>
+        <v>-0.206599944744578</v>
       </c>
     </row>
     <row r="829">
@@ -10123,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.555678622906218</v>
+        <v>-0.147094971779842</v>
       </c>
     </row>
     <row r="830">
@@ -10134,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.167239692070617</v>
+        <v>-0.175206767033892</v>
       </c>
     </row>
     <row r="831">
@@ -10145,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.183103970478787</v>
+        <v>-0.0970138050442124</v>
       </c>
     </row>
     <row r="832">
@@ -10167,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.366766018927544</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="834">
@@ -10189,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.630591584985488</v>
+        <v>-0.439266518701433</v>
       </c>
     </row>
     <row r="836">
@@ -10200,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.440983362810629</v>
+        <v>-0.247538266878609</v>
       </c>
     </row>
     <row r="837">
@@ -10211,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.260545408209902</v>
+        <v>-0.642341123807568</v>
       </c>
     </row>
     <row r="838">
@@ -10233,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.428744431535566</v>
+        <v>-0.302773864318827</v>
       </c>
     </row>
     <row r="840">
@@ -10255,7 +10249,7 @@
         <v>16</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.214734732944997</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="842">
@@ -10277,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.737961572469234</v>
+        <v>-0.247084648408409</v>
       </c>
     </row>
     <row r="844">
@@ -10288,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.198414240364323</v>
+        <v>-0.217946084809103</v>
       </c>
     </row>
     <row r="845">
@@ -10321,7 +10315,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.193888106884037</v>
+        <v>-0.238041468317117</v>
       </c>
     </row>
     <row r="848">
@@ -10332,7 +10326,7 @@
         <v>16</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.19324035504258</v>
+        <v>-0.216161563857034</v>
       </c>
     </row>
     <row r="849">
@@ -10343,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.853599282510622</v>
+        <v>-0.181533021427202</v>
       </c>
     </row>
     <row r="850">
@@ -10354,7 +10348,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.53793051828402</v>
       </c>
     </row>
     <row r="851">
@@ -10365,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.410244840307162</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="852">
@@ -10376,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.169117984807306</v>
+        <v>-0.727210690815671</v>
       </c>
     </row>
     <row r="853">
@@ -10398,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.285870952849353</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="855">
@@ -10409,7 +10403,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.798858568429232</v>
+        <v>-0.238287479532988</v>
       </c>
     </row>
     <row r="856">
@@ -10420,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.245614239220644</v>
+        <v>-0.261018956909872</v>
       </c>
     </row>
     <row r="857">
@@ -10431,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.56171214470749</v>
       </c>
     </row>
     <row r="858">
@@ -10442,7 +10436,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.213809550893609</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="859">
@@ -10453,7 +10447,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-1.22799169593691</v>
+        <v>-0.591824125818482</v>
       </c>
     </row>
     <row r="860">
@@ -10464,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.397127206664149</v>
+        <v>-0.399162638787389</v>
       </c>
     </row>
     <row r="861">
@@ -10475,7 +10469,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.151410608119014</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="862">
@@ -10486,7 +10480,7 @@
         <v>16</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.174316845712335</v>
+        <v>-0.584654680349748</v>
       </c>
     </row>
     <row r="863">
@@ -10497,7 +10491,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.325790323346854</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="864">
@@ -10508,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.451915679874417</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="865">
@@ -10530,7 +10524,7 @@
         <v>16</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.14795918367347</v>
+        <v>-7.01187093816788</v>
       </c>
     </row>
     <row r="867">
@@ -10541,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.80173069552326</v>
       </c>
     </row>
     <row r="868">
@@ -10563,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.215685636368149</v>
+        <v>-0.301882293686915</v>
       </c>
     </row>
     <row r="870">
@@ -10585,7 +10579,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-1.08766219185321</v>
+        <v>-0.30139670532159</v>
       </c>
     </row>
     <row r="872">
@@ -10596,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.204062826216007</v>
+        <v>-0.224649755870066</v>
       </c>
     </row>
     <row r="873">
@@ -10629,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.295444717219519</v>
+        <v>-0.302983397026557</v>
       </c>
     </row>
     <row r="876">
@@ -10640,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-2.47237498243598</v>
+        <v>0.369171458191795</v>
       </c>
     </row>
     <row r="877">
@@ -10651,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.239350101624287</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="878">
@@ -10673,7 +10667,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.190102644515905</v>
       </c>
     </row>
     <row r="880">
@@ -10684,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.488296205539896</v>
+        <v>-0.299346432878615</v>
       </c>
     </row>
     <row r="881">
@@ -10695,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.99800740871666</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="882">
@@ -10706,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.29640100303721</v>
       </c>
     </row>
     <row r="883">
@@ -10717,7 +10711,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.40115500542395</v>
       </c>
     </row>
     <row r="884">
@@ -10728,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.257961696490541</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="885">
@@ -10739,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.291491663905158</v>
+        <v>-0.161084882548656</v>
       </c>
     </row>
     <row r="886">
@@ -10750,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.275516972123254</v>
       </c>
     </row>
     <row r="887">
@@ -10772,7 +10766,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-1.07563306419514</v>
+        <v>-0.861309105203028</v>
       </c>
     </row>
     <row r="889">
@@ -10783,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.160967117055899</v>
+        <v>-1.29429372182298</v>
       </c>
     </row>
     <row r="890">
@@ -10805,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>0.021637329400455</v>
+        <v>0.26737840640765</v>
       </c>
     </row>
     <row r="892">
@@ -10816,7 +10810,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>0.0209313664207464</v>
+        <v>-0.219443378956909</v>
       </c>
     </row>
     <row r="893">
@@ -10827,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.179791122964813</v>
+        <v>-0.270902937700498</v>
       </c>
     </row>
     <row r="894">
@@ -10838,7 +10832,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.837432471254752</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="895">
@@ -10860,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-1.07284975771687</v>
+        <v>-1.00575390179256</v>
       </c>
     </row>
     <row r="897">
@@ -10871,7 +10865,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.195023059430825</v>
+        <v>-0.443550525196768</v>
       </c>
     </row>
     <row r="898">
@@ -10893,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.0697662824744796</v>
+        <v>0.0399242848116091</v>
       </c>
     </row>
     <row r="900">
@@ -10904,7 +10898,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.601774733382109</v>
+        <v>-0.489684963740998</v>
       </c>
     </row>
     <row r="901">
@@ -10915,7 +10909,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.382258685272304</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="902">
@@ -10926,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.247023981032076</v>
+        <v>-0.173951638755837</v>
       </c>
     </row>
     <row r="903">
@@ -10937,7 +10931,7 @@
         <v>16</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.556539730315445</v>
+        <v>-0.163612035716785</v>
       </c>
     </row>
     <row r="904">
@@ -10948,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.950671620490649</v>
+        <v>-2.43630845459902</v>
       </c>
     </row>
     <row r="905">
@@ -10970,7 +10964,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.527484693258536</v>
+        <v>-0.231450055858212</v>
       </c>
     </row>
     <row r="907">
@@ -10981,7 +10975,7 @@
         <v>16</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.329390356371649</v>
+        <v>-0.789465764338835</v>
       </c>
     </row>
     <row r="908">
@@ -10992,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.322918163489118</v>
+        <v>-0.546911115510064</v>
       </c>
     </row>
     <row r="909">
@@ -11003,7 +10997,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.474609945911801</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="910">
@@ -11014,7 +11008,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.309548364206676</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="911">
@@ -11025,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.550425255327957</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="912">
@@ -11069,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.268069496383802</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="916">
@@ -11080,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.390073284791881</v>
+        <v>-0.253858363998575</v>
       </c>
     </row>
     <row r="917">
@@ -11091,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.285921372634665</v>
+        <v>-0.308771155143367</v>
       </c>
     </row>
     <row r="918">
@@ -11113,7 +11107,7 @@
         <v>16</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.681511765581904</v>
+        <v>-17.6608082899572</v>
       </c>
     </row>
     <row r="920">
@@ -11124,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.382263202903066</v>
+        <v>-1.54531066761552</v>
       </c>
     </row>
     <row r="921">
@@ -11157,7 +11151,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.334066540643058</v>
       </c>
     </row>
     <row r="924">
@@ -11168,7 +11162,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.209269494062826</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="925">
@@ -11179,7 +11173,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.261572663726939</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="926">
@@ -11190,7 +11184,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.416690274126314</v>
+        <v>-0.629447203238969</v>
       </c>
     </row>
     <row r="927">
@@ -11201,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.171566705122074</v>
+        <v>-0.286995402599853</v>
       </c>
     </row>
     <row r="928">
@@ -11212,7 +11206,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.372416538981638</v>
+        <v>-0.2032233123133</v>
       </c>
     </row>
     <row r="929">
@@ -11223,7 +11217,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.274604773783219</v>
       </c>
     </row>
     <row r="930">
@@ -11245,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.14795918367347</v>
+        <v>-11.7471055662333</v>
       </c>
     </row>
     <row r="932">
@@ -11256,7 +11250,7 @@
         <v>16</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.23643835491717</v>
+        <v>-0.15837097572601</v>
       </c>
     </row>
     <row r="933">
@@ -11267,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.285178554488305</v>
+        <v>-0.595001507236468</v>
       </c>
     </row>
     <row r="934">
@@ -11278,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.736769335568648</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="935">
@@ -11289,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.390463695703289</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="936">
@@ -11300,7 +11294,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.135883382296183</v>
+        <v>-0.155799573709474</v>
       </c>
     </row>
     <row r="937">
@@ -11322,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.144709296929753</v>
+        <v>-0.849514343924681</v>
       </c>
     </row>
     <row r="939">
@@ -11333,7 +11327,7 @@
         <v>16</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.85508283384753</v>
       </c>
     </row>
     <row r="940">
@@ -11344,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.309638164547351</v>
+        <v>-0.228502143564819</v>
       </c>
     </row>
     <row r="941">
@@ -11355,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>0.0611127736009804</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="942">
@@ -11366,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.485973502623932</v>
+        <v>-0.278157758704748</v>
       </c>
     </row>
     <row r="943">
@@ -11377,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.403096674793422</v>
+        <v>-0.246200436213306</v>
       </c>
     </row>
     <row r="944">
@@ -11388,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.60075296097643</v>
       </c>
     </row>
     <row r="945">
@@ -11399,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>0.00105404493580707</v>
+        <v>-0.00677146180750388</v>
       </c>
     </row>
     <row r="946">
@@ -11410,7 +11404,7 @@
         <v>16</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.272600221927183</v>
+        <v>-0.229189050804381</v>
       </c>
     </row>
     <row r="947">
@@ -11421,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.146573555639638</v>
+        <v>-0.0474765217698314</v>
       </c>
     </row>
     <row r="948">
@@ -11432,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.606376620175806</v>
+        <v>-0.832934435571801</v>
       </c>
     </row>
     <row r="949">
@@ -11443,7 +11437,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>0.190607636475545</v>
+        <v>-0.135088035562808</v>
       </c>
     </row>
     <row r="950">
@@ -11465,7 +11459,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>0.270662936083408</v>
+        <v>0.0100958885251037</v>
       </c>
     </row>
     <row r="952">
@@ -11476,7 +11470,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.496427369802753</v>
+        <v>-4.51605728648945</v>
       </c>
     </row>
     <row r="953">
@@ -11487,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.777586900130121</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="954">
@@ -11509,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-1.44163371021619</v>
+        <v>-0.191583424163003</v>
       </c>
     </row>
     <row r="956">
@@ -11520,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.206236321690956</v>
+        <v>-0.243423441191086</v>
       </c>
     </row>
     <row r="957">
@@ -11542,7 +11536,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.115343150781027</v>
+        <v>-1.48782503060767</v>
       </c>
     </row>
     <row r="959">
@@ -11586,7 +11580,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.311166293523692</v>
+        <v>-0.243709393767989</v>
       </c>
     </row>
     <row r="963">
@@ -11597,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.176111758979623</v>
+        <v>-0.201271484919595</v>
       </c>
     </row>
     <row r="964">
@@ -11619,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.265152332891617</v>
+        <v>-0.137306809436903</v>
       </c>
     </row>
     <row r="966">
@@ -11630,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.372118332344734</v>
+        <v>-0.529430585318983</v>
       </c>
     </row>
     <row r="967">
@@ -11641,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.734433113103863</v>
+        <v>-1.02375872904232</v>
       </c>
     </row>
     <row r="968">
@@ -11663,7 +11657,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.219177038205896</v>
+        <v>-0.180046127027616</v>
       </c>
     </row>
     <row r="970">
@@ -11674,7 +11668,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.187190535461098</v>
+        <v>-0.157602707705351</v>
       </c>
     </row>
     <row r="971">
@@ -11685,7 +11679,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-1.08970487441124</v>
+        <v>-0.504039627287279</v>
       </c>
     </row>
     <row r="972">
@@ -11707,7 +11701,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.419660733250907</v>
+        <v>-0.494139465662547</v>
       </c>
     </row>
     <row r="974">
@@ -11718,7 +11712,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-1.05846528324108</v>
+        <v>-0.447232687363062</v>
       </c>
     </row>
     <row r="975">
@@ -11751,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.161530221330424</v>
+        <v>-1.89913849348295</v>
       </c>
     </row>
     <row r="978">
@@ -11762,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.213131450398366</v>
+        <v>-0.178647091835386</v>
       </c>
     </row>
     <row r="979">
@@ -11773,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-4.44165469538055</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="980">
@@ -11784,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.323660687949499</v>
+        <v>-0.457538852263153</v>
       </c>
     </row>
     <row r="981">
@@ -11795,7 +11789,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.100115038610262</v>
+        <v>-0.223030016262497</v>
       </c>
     </row>
     <row r="982">
@@ -11806,7 +11800,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.611697784155923</v>
+        <v>-1.93494284388131</v>
       </c>
     </row>
     <row r="983">
@@ -11828,7 +11822,7 @@
         <v>16</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.469833010344934</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="985">
@@ -11839,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.17266805748148</v>
+        <v>-0.339286276134297</v>
       </c>
     </row>
     <row r="986">
@@ -11850,7 +11844,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-2.09427817411354</v>
+        <v>-0.34025425028605</v>
       </c>
     </row>
     <row r="987">
@@ -11861,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.375896792418448</v>
+        <v>-0.66459347035047</v>
       </c>
     </row>
     <row r="988">
@@ -11872,7 +11866,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.212286877601122</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="989">
@@ -11883,7 +11877,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.318881774648199</v>
+        <v>-0.699945897950778</v>
       </c>
     </row>
     <row r="990">
@@ -11894,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.18020971476566</v>
+        <v>-0.202794203520835</v>
       </c>
     </row>
     <row r="991">
@@ -11905,7 +11899,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.352814835102759</v>
+        <v>-1.00604239222273</v>
       </c>
     </row>
     <row r="992">
@@ -11916,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.23881708301587</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="993">
@@ -11927,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.319955250853448</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="994">
@@ -11949,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.432443177156649</v>
+        <v>-1.31945808452672</v>
       </c>
     </row>
     <row r="996">
@@ -11982,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.152131864630303</v>
+        <v>-0.0374154083582976</v>
       </c>
     </row>
     <row r="999">
@@ -11993,7 +11987,7 @@
         <v>16</v>
       </c>
       <c r="C999" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.00483981258921</v>
       </c>
     </row>
     <row r="1000">
@@ -12004,7 +11998,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-1.08199750064173</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="1001">
@@ -12015,7 +12009,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.235101850828309</v>
       </c>
     </row>
     <row r="1002">
@@ -12026,7 +12020,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.310555048082619</v>
+        <v>-0.240121644431178</v>
       </c>
     </row>
     <row r="1003">
@@ -12048,7 +12042,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.883697965163841</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1005">
@@ -12070,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.0317856625052275</v>
+        <v>-0.271760938201792</v>
       </c>
     </row>
     <row r="1007">
@@ -12081,7 +12075,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.270163496760528</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1008">
@@ -12092,7 +12086,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.419640451912203</v>
       </c>
     </row>
     <row r="1009">
@@ -12114,7 +12108,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.544855154892324</v>
+        <v>-0.96247675807318</v>
       </c>
     </row>
     <row r="1011">
@@ -12136,7 +12130,7 @@
         <v>16</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.28692505284118</v>
+        <v>-0.22828740645</v>
       </c>
     </row>
     <row r="1013">
@@ -12147,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.297549565638142</v>
+        <v>-0.869584372206847</v>
       </c>
     </row>
     <row r="1014">
@@ -12158,7 +12152,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.456924727785978</v>
       </c>
     </row>
     <row r="1015">
@@ -12169,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.443586233247366</v>
+        <v>-0.425703692332458</v>
       </c>
     </row>
     <row r="1016">
@@ -12180,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.260677921073321</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1017">
@@ -12191,7 +12185,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.768123306224018</v>
       </c>
     </row>
     <row r="1018">
@@ -12213,7 +12207,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.19291231337606</v>
+        <v>-0.313824086758709</v>
       </c>
     </row>
     <row r="1020">
@@ -12224,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.06400405969786</v>
       </c>
     </row>
     <row r="1021">
@@ -12257,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.202249679598184</v>
+        <v>-0.118877313256323</v>
       </c>
     </row>
     <row r="1024">
@@ -12268,7 +12262,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.172573592528457</v>
+        <v>-0.16982931369149</v>
       </c>
     </row>
     <row r="1025">
@@ -12279,7 +12273,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.185559438336728</v>
       </c>
     </row>
     <row r="1026">
@@ -12301,7 +12295,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.949277047885203</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1028">
@@ -12312,7 +12306,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.370746339273585</v>
+        <v>-0.441841997979859</v>
       </c>
     </row>
     <row r="1029">
@@ -12323,7 +12317,7 @@
         <v>16</v>
       </c>
       <c r="C1029" t="n">
-        <v>-0.160507999916901</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1030">
@@ -12334,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.405878530625207</v>
+        <v>-0.205068588530366</v>
       </c>
     </row>
     <row r="1031">
@@ -12356,7 +12350,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-1.28186992665649</v>
+        <v>-0.4143083738123</v>
       </c>
     </row>
     <row r="1033">
@@ -12367,7 +12361,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.201887954879708</v>
       </c>
     </row>
     <row r="1034">
@@ -12378,7 +12372,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.33949920076771</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1035">
@@ -12400,7 +12394,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.260385757946481</v>
       </c>
     </row>
     <row r="1037">
@@ -12411,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.167055925913658</v>
+        <v>0.249089200081809</v>
       </c>
     </row>
     <row r="1038">
@@ -12422,7 +12416,7 @@
         <v>16</v>
       </c>
       <c r="C1038" t="n">
-        <v>-0.183512237814426</v>
+        <v>-0.192829606341054</v>
       </c>
     </row>
     <row r="1039">
@@ -12433,7 +12427,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.65179854145035</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1040">
@@ -12444,7 +12438,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.208187854857714</v>
+        <v>-0.193119234853624</v>
       </c>
     </row>
     <row r="1041">
@@ -12455,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.289137866556642</v>
+        <v>-0.23603634497838</v>
       </c>
     </row>
     <row r="1042">
@@ -12466,7 +12460,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.6557665248404</v>
       </c>
     </row>
     <row r="1043">
@@ -12477,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.424363509482284</v>
+        <v>-0.733013513144121</v>
       </c>
     </row>
     <row r="1044">
@@ -12488,7 +12482,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.216625882487236</v>
+        <v>-0.27033342999584</v>
       </c>
     </row>
     <row r="1045">
@@ -12510,7 +12504,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.235899448965707</v>
+        <v>-0.195621713797472</v>
       </c>
     </row>
     <row r="1047">
@@ -12521,7 +12515,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.341410885696754</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1048">
@@ -12532,7 +12526,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.504296565787389</v>
+        <v>-0.100478419443893</v>
       </c>
     </row>
     <row r="1049">
@@ -12554,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.353278491152742</v>
+        <v>-0.258655173871636</v>
       </c>
     </row>
     <row r="1051">
@@ -12565,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.352035348066115</v>
       </c>
     </row>
     <row r="1052">
@@ -12587,7 +12581,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.179967243487248</v>
+        <v>-0.690913859551593</v>
       </c>
     </row>
     <row r="1054">
@@ -12609,7 +12603,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-1.13456568338938</v>
+        <v>-0.359696059137566</v>
       </c>
     </row>
     <row r="1056">
@@ -12653,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-1.22867284012013</v>
+        <v>-0.21362620422926</v>
       </c>
     </row>
     <row r="1060">
@@ -12664,7 +12658,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.280889084086537</v>
+        <v>-0.154663078900715</v>
       </c>
     </row>
     <row r="1061">
@@ -12675,7 +12669,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.176409924615666</v>
+        <v>-0.23024886757039</v>
       </c>
     </row>
     <row r="1062">
@@ -12686,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.21613896572185</v>
       </c>
     </row>
     <row r="1063">
@@ -12697,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.122816021868254</v>
+        <v>-0.179550872490355</v>
       </c>
     </row>
     <row r="1064">
@@ -12708,7 +12702,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.150875589304588</v>
+        <v>-0.616622986179014</v>
       </c>
     </row>
     <row r="1065">
@@ -12730,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.123918308837097</v>
+        <v>-0.099945198480843</v>
       </c>
     </row>
     <row r="1067">
@@ -12763,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.159763313609468</v>
+        <v>-3.15561535745923</v>
       </c>
     </row>
     <row r="1070">
@@ -12785,7 +12779,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.253736647268146</v>
+        <v>-0.0305599143085542</v>
       </c>
     </row>
     <row r="1072">
@@ -12796,7 +12790,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.213489732897388</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1073">
@@ -12807,7 +12801,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.436987809124367</v>
       </c>
     </row>
     <row r="1074">
@@ -12818,7 +12812,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.205724833783397</v>
+        <v>-0.207194466337203</v>
       </c>
     </row>
     <row r="1075">
@@ -12851,7 +12845,7 @@
         <v>16</v>
       </c>
       <c r="C1077" t="n">
-        <v>-2.06222230325381</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1078">
@@ -12906,7 +12900,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.212465626930761</v>
+        <v>-1.74484266129054</v>
       </c>
     </row>
     <row r="1083">
@@ -12917,7 +12911,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.681116331136855</v>
+        <v>-0.182798470382079</v>
       </c>
     </row>
     <row r="1084">
@@ -12939,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.407110488708749</v>
+        <v>-0.587713842549543</v>
       </c>
     </row>
     <row r="1086">
@@ -12950,7 +12944,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.335339413240163</v>
+        <v>-0.286569035362061</v>
       </c>
     </row>
     <row r="1087">
@@ -12961,7 +12955,7 @@
         <v>16</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.220969611487708</v>
+        <v>-1.24149255213868</v>
       </c>
     </row>
     <row r="1088">
@@ -12972,7 +12966,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>0.019272870047677</v>
+        <v>0.0960308138754229</v>
       </c>
     </row>
     <row r="1089">
@@ -12983,7 +12977,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.138529009982511</v>
+        <v>-0.692123216763876</v>
       </c>
     </row>
     <row r="1090">
@@ -12994,7 +12988,7 @@
         <v>16</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.945414393571888</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1091">
@@ -13016,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.232247907497374</v>
+        <v>-1.96566029732823</v>
       </c>
     </row>
     <row r="1093">
@@ -13027,7 +13021,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.58991530889216</v>
+        <v>-1.27924488649264</v>
       </c>
     </row>
     <row r="1094">
@@ -13049,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.583413353781599</v>
+        <v>-0.485291432260363</v>
       </c>
     </row>
     <row r="1096">
@@ -13071,7 +13065,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.225433665706521</v>
+        <v>-1.93529798728145</v>
       </c>
     </row>
     <row r="1098">
@@ -13082,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>0.0691646317564694</v>
+        <v>-0.190126882266388</v>
       </c>
     </row>
     <row r="1099">
@@ -13093,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.173356024210077</v>
+        <v>-0.147895268236705</v>
       </c>
     </row>
     <row r="1100">
@@ -13104,7 +13098,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>-0.169206321398323</v>
+        <v>-1.30260249874287</v>
       </c>
     </row>
     <row r="1101">
@@ -13115,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-1.0518238441253</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1102">
@@ -13137,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.0316799791797958</v>
+        <v>-0.117525820756399</v>
       </c>
     </row>
     <row r="1104">
@@ -13148,7 +13142,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.159763313609467</v>
+        <v>-6.55508338026155</v>
       </c>
     </row>
     <row r="1105">
@@ -13159,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.91529884378311</v>
       </c>
     </row>
     <row r="1106">
@@ -13170,7 +13164,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.212546354082278</v>
+        <v>-0.267998877087956</v>
       </c>
     </row>
     <row r="1107">
@@ -13181,7 +13175,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.523615297485676</v>
+        <v>-0.420094193436231</v>
       </c>
     </row>
     <row r="1108">
@@ -13192,7 +13186,7 @@
         <v>16</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.316091222284255</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1109">
@@ -13203,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-1.28259855802344</v>
+        <v>-0.25952269754254</v>
       </c>
     </row>
     <row r="1110">
@@ -13236,7 +13230,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.33387611100094</v>
       </c>
     </row>
     <row r="1113">
@@ -13247,7 +13241,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.307321623062878</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1114">
@@ -13258,7 +13252,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.31475802975454</v>
       </c>
     </row>
     <row r="1115">
@@ -13269,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.0204530511174568</v>
+        <v>0.405763220509806</v>
       </c>
     </row>
     <row r="1116">
@@ -13291,7 +13285,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.359478034712806</v>
+        <v>-0.278838530333272</v>
       </c>
     </row>
     <row r="1118">
@@ -13313,7 +13307,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.301975265134478</v>
       </c>
     </row>
     <row r="1120">
@@ -13324,7 +13318,7 @@
         <v>16</v>
       </c>
       <c r="C1120" t="n">
-        <v>-0.466704699249139</v>
+        <v>-0.42657410534483</v>
       </c>
     </row>
     <row r="1121">
@@ -13379,7 +13373,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.643863580403811</v>
+        <v>0.266882332419061</v>
       </c>
     </row>
     <row r="1126">
@@ -13401,7 +13395,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.312046124541146</v>
+        <v>-0.540539126795039</v>
       </c>
     </row>
     <row r="1128">
@@ -13412,7 +13406,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.453367445301011</v>
+        <v>-0.761175323825218</v>
       </c>
     </row>
     <row r="1129">
@@ -13434,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.231887064903583</v>
+        <v>-0.546178469410731</v>
       </c>
     </row>
     <row r="1131">
@@ -13445,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.265958219354565</v>
+        <v>-0.237094644352137</v>
       </c>
     </row>
     <row r="1132">
@@ -13456,7 +13450,7 @@
         <v>16</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.031785145838453</v>
+        <v>-0.226736644409382</v>
       </c>
     </row>
     <row r="1133">
@@ -13467,7 +13461,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.381430069755253</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1134">
@@ -13500,7 +13494,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.160722213049514</v>
+        <v>-0.159267306547571</v>
       </c>
     </row>
     <row r="1137">
@@ -13511,7 +13505,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.028090654592646</v>
+        <v>-0.214403843140351</v>
       </c>
     </row>
     <row r="1138">
@@ -13533,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.300536782640666</v>
+        <v>-0.10929110805903</v>
       </c>
     </row>
     <row r="1140">
@@ -13544,7 +13538,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.403720933651117</v>
       </c>
     </row>
     <row r="1141">
@@ -13555,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-1.01042208696026</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1142">
@@ -13566,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.186313055318578</v>
+        <v>-0.185515585577418</v>
       </c>
     </row>
     <row r="1143">
@@ -13577,7 +13571,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.275103021355621</v>
+        <v>-0.242027810711539</v>
       </c>
     </row>
     <row r="1144">
@@ -13599,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.250786171547847</v>
+        <v>-0.425023492639708</v>
       </c>
     </row>
     <row r="1146">
@@ -13610,7 +13604,7 @@
         <v>16</v>
       </c>
       <c r="C1146" t="n">
-        <v>-0.317981870877667</v>
+        <v>-0.206182605625283</v>
       </c>
     </row>
     <row r="1147">
@@ -13621,7 +13615,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.525509542285306</v>
+        <v>-0.553309909510414</v>
       </c>
     </row>
     <row r="1148">
@@ -13643,7 +13637,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.602631477639419</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1150">
@@ -13654,7 +13648,7 @@
         <v>16</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.159763313609467</v>
+        <v>-3.23221715652857</v>
       </c>
     </row>
     <row r="1151">
@@ -13676,7 +13670,7 @@
         <v>16</v>
       </c>
       <c r="C1152" t="n">
-        <v>-0.445562751045057</v>
+        <v>-1.72078137372356</v>
       </c>
     </row>
     <row r="1153">
@@ -13709,7 +13703,7 @@
         <v>16</v>
       </c>
       <c r="C1155" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.648752369225763</v>
       </c>
     </row>
     <row r="1156">
@@ -13720,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.17894620192231</v>
+        <v>-0.715622229546482</v>
       </c>
     </row>
     <row r="1157">
@@ -13742,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.190462589490785</v>
+        <v>-0.14564982805771</v>
       </c>
     </row>
     <row r="1159">
@@ -13764,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.388742068111509</v>
+        <v>-0.547278336719165</v>
       </c>
     </row>
     <row r="1161">
@@ -13775,7 +13769,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.0795446892407935</v>
+        <v>-0.381204690960569</v>
       </c>
     </row>
     <row r="1162">
@@ -13797,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.346579830809854</v>
+        <v>-1.26417322167937</v>
       </c>
     </row>
     <row r="1164">
@@ -13830,7 +13824,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.823191408695441</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1167">
@@ -13841,7 +13835,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.442354371804349</v>
+        <v>-0.254902245208953</v>
       </c>
     </row>
     <row r="1168">
@@ -13852,7 +13846,7 @@
         <v>16</v>
       </c>
       <c r="C1168" t="n">
-        <v>-0.186390923129246</v>
+        <v>-0.204298002610151</v>
       </c>
     </row>
     <row r="1169">
@@ -13874,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.268087536291753</v>
+        <v>0.497612293593777</v>
       </c>
     </row>
     <row r="1171">
@@ -13907,7 +13901,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.241362421179707</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1174">
@@ -13929,7 +13923,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.213872188519436</v>
+        <v>-0.381667937653424</v>
       </c>
     </row>
     <row r="1176">
@@ -13940,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.65685940730064</v>
       </c>
     </row>
     <row r="1177">
@@ -13962,7 +13956,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.220710025677186</v>
+        <v>-0.228005018694463</v>
       </c>
     </row>
     <row r="1179">
@@ -13973,7 +13967,7 @@
         <v>16</v>
       </c>
       <c r="C1179" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.279547029582274</v>
       </c>
     </row>
     <row r="1180">
@@ -13984,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.396555475317958</v>
+        <v>-0.900695203942399</v>
       </c>
     </row>
     <row r="1181">
@@ -14028,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.122035311448919</v>
+        <v>0.0661945760318144</v>
       </c>
     </row>
     <row r="1185">
@@ -14039,7 +14033,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.59504464670349</v>
+        <v>-0.307383601742226</v>
       </c>
     </row>
     <row r="1186">
@@ -14050,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.409945508091138</v>
+        <v>0.577759132752799</v>
       </c>
     </row>
     <row r="1187">
@@ -14061,7 +14055,7 @@
         <v>16</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.346681462198232</v>
+        <v>-0.286781858653591</v>
       </c>
     </row>
     <row r="1188">
@@ -14072,7 +14066,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.226056870937285</v>
+        <v>-0.183793837287838</v>
       </c>
     </row>
     <row r="1189">
@@ -14083,7 +14077,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.20441334389637</v>
+        <v>-1.13346800293339</v>
       </c>
     </row>
     <row r="1190">
@@ -14094,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.359698599929495</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1191">
@@ -14105,7 +14099,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.332615548896838</v>
       </c>
     </row>
     <row r="1192">
@@ -14116,7 +14110,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.425915300255149</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1193">
@@ -14127,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-3.35025180894137</v>
+        <v>-1.10387272905607</v>
       </c>
     </row>
     <row r="1194">
@@ -14138,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-1.1330724062096</v>
+        <v>-0.734675374786828</v>
       </c>
     </row>
     <row r="1195">
@@ -14160,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.161704139395537</v>
+        <v>0.104368121241032</v>
       </c>
     </row>
     <row r="1197">
@@ -14171,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.319697433723878</v>
+        <v>-0.0256268082559534</v>
       </c>
     </row>
     <row r="1198">
@@ -14182,7 +14176,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-0.148325881970448</v>
+        <v>-0.0905372779467077</v>
       </c>
     </row>
     <row r="1199">
@@ -14193,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.226164721954934</v>
+        <v>-0.253051762944793</v>
       </c>
     </row>
     <row r="1200">
@@ -14204,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.249362806370468</v>
+        <v>-0.184385874129711</v>
       </c>
     </row>
     <row r="1201">
@@ -14215,7 +14209,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.346393356743</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
   </sheetData>
@@ -14277,7 +14271,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2013264349888</v>
+        <v>3.18752211281303</v>
       </c>
     </row>
     <row r="4">
@@ -14294,7 +14288,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>4.23357142857143</v>
+        <v>2.59377580225107</v>
       </c>
     </row>
     <row r="5">
@@ -14413,7 +14407,7 @@
         <v>-4.09</v>
       </c>
       <c r="E11" t="n">
-        <v>5.50357142857143</v>
+        <v>4.9433198221949</v>
       </c>
     </row>
     <row r="12">
@@ -14447,7 +14441,7 @@
         <v>-1.86</v>
       </c>
       <c r="E13" t="n">
-        <v>8.58420616122105</v>
+        <v>5.34428571428571</v>
       </c>
     </row>
     <row r="14">
@@ -14549,7 +14543,7 @@
         <v>1924.77</v>
       </c>
       <c r="E19" t="n">
-        <v>-348.487857142857</v>
+        <v>-2035.74128536722</v>
       </c>
     </row>
     <row r="20">
@@ -15025,7 +15019,7 @@
         <v>1.706</v>
       </c>
       <c r="E47" t="n">
-        <v>1.50538186715789</v>
+        <v>1.99364285714286</v>
       </c>
     </row>
     <row r="48">
@@ -15042,7 +15036,7 @@
         <v>4.218</v>
       </c>
       <c r="E48" t="n">
-        <v>1.70389615090679</v>
+        <v>1.81421428571429</v>
       </c>
     </row>
     <row r="49">
@@ -15059,7 +15053,7 @@
         <v>1.578</v>
       </c>
       <c r="E49" t="n">
-        <v>1.23958496325347</v>
+        <v>2.00278571428571</v>
       </c>
     </row>
     <row r="50">
@@ -15076,7 +15070,7 @@
         <v>3.683</v>
       </c>
       <c r="E50" t="n">
-        <v>4.862388175128</v>
+        <v>1.85242857142857</v>
       </c>
     </row>
     <row r="51">
@@ -15093,7 +15087,7 @@
         <v>2.983</v>
       </c>
       <c r="E51" t="n">
-        <v>4.98296099857703</v>
+        <v>1.90242857142857</v>
       </c>
     </row>
     <row r="52">
@@ -15110,7 +15104,7 @@
         <v>2.44</v>
       </c>
       <c r="E52" t="n">
-        <v>2.80752293323819</v>
+        <v>1.94121428571429</v>
       </c>
     </row>
     <row r="53">
@@ -15127,7 +15121,7 @@
         <v>3.879</v>
       </c>
       <c r="E53" t="n">
-        <v>5.94884183860137</v>
+        <v>1.83842857142857</v>
       </c>
     </row>
     <row r="54">
@@ -15144,7 +15138,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E54" t="n">
-        <v>1.54341181548512</v>
+        <v>2.07407142857143</v>
       </c>
     </row>
     <row r="55">
@@ -15161,7 +15155,7 @@
         <v>-1.918</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.725666547037378</v>
+        <v>2.2525</v>
       </c>
     </row>
     <row r="56">
@@ -15178,7 +15172,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>1.29572570251438</v>
+        <v>2.0675</v>
       </c>
     </row>
     <row r="57">
@@ -15195,7 +15189,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E57" t="n">
-        <v>0.179450950998231</v>
+        <v>-0.755400637293123</v>
       </c>
     </row>
     <row r="58">
@@ -15212,7 +15206,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>4.20417018861664</v>
+        <v>1.752</v>
       </c>
     </row>
     <row r="59">
@@ -15229,7 +15223,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>1.65132591381167</v>
+        <v>5.65040555794002</v>
       </c>
     </row>
     <row r="60">
@@ -15246,7 +15240,7 @@
         <v>1.311</v>
       </c>
       <c r="E60" t="n">
-        <v>1.78938832520897</v>
+        <v>2.02185714285714</v>
       </c>
     </row>
     <row r="61">
@@ -15263,7 +15257,7 @@
         <v>2.862</v>
       </c>
       <c r="E61" t="n">
-        <v>1.35539392945842</v>
+        <v>1.91107142857143</v>
       </c>
     </row>
     <row r="62">
@@ -15314,7 +15308,7 @@
         <v>90</v>
       </c>
       <c r="E64" t="n">
-        <v>7.77003754107551</v>
+        <v>37.8571428571429</v>
       </c>
     </row>
     <row r="65">
@@ -15798,10 +15792,10 @@
         <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -15815,10 +15809,10 @@
         <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -15832,10 +15826,10 @@
         <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -15857,7 +15851,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -15874,7 +15868,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -15891,13 +15885,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -15908,13 +15902,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -15925,121 +15919,121 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.866666666666667</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.466666666666667</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.333333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.333333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -16050,13 +16044,13 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.333333333333333</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -16067,13 +16061,13 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.266666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -16084,13 +16078,13 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>0.266666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -16101,13 +16095,13 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -16118,103 +16112,103 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
@@ -16223,112 +16217,10 @@
         <v>53</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="s">
-        <v>50</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
   </sheetData>
